--- a/resources/reference.xlsx
+++ b/resources/reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD66D4A-6CE1-4B08-B4B8-F9BCA4205773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63845B0C-181F-442F-A798-8259E2C60691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
   </bookViews>
   <sheets>
     <sheet name="objectives" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="229">
   <si>
     <t>Demographics</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Health Needs</t>
   </si>
   <si>
-    <t>To estimate the proportion of the population with health care needs in the two weeks prior to data collection (any health care needs, unmet needs, needs by sex/age/symptom)</t>
-  </si>
-  <si>
     <t>To understand the main barriers for the target population in accessing health and nutrition services.</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t>To estimate the proportion of children 6-59 months of age severely or moderately acutely malnourished by MUAC.</t>
-  </si>
-  <si>
-    <t>To estimate the proportion of pregnant and lactating women 15-49 years of age severely or moderately acutely malnourished by MUAC.</t>
   </si>
   <si>
     <t>To estimate the coverage of Vitamin A supplementation among children 6-59 months of age</t>
@@ -374,9 +368,6 @@
     <t>NutritionStatus</t>
   </si>
   <si>
-    <t>GAM by MUAC for Pregnant and Lactating Women</t>
-  </si>
-  <si>
     <t>GAM by MUAC for Children 6-59 Months Old</t>
   </si>
   <si>
@@ -488,24 +479,12 @@
     <t>Sex Ratio</t>
   </si>
   <si>
-    <t>% of Children Under-5</t>
-  </si>
-  <si>
     <t>Average Household Size</t>
   </si>
   <si>
     <t>Mean Age (years)</t>
   </si>
   <si>
-    <t>Age Category, 5-year bins</t>
-  </si>
-  <si>
-    <t>Age Category, 6-month bins</t>
-  </si>
-  <si>
-    <t>The ratio of males to females in the assessed population</t>
-  </si>
-  <si>
     <t># of males</t>
   </si>
   <si>
@@ -518,9 +497,6 @@
     <t>Total Population Size</t>
   </si>
   <si>
-    <t>Number of individuals</t>
-  </si>
-  <si>
     <t>Total Number of Pregnant and Lactating Women</t>
   </si>
   <si>
@@ -536,25 +512,235 @@
     <t>Total Number of Children Under-2</t>
   </si>
   <si>
-    <t>Number of pregnant and lactating women</t>
-  </si>
-  <si>
-    <t>Number of children under 2 years of age</t>
-  </si>
-  <si>
-    <t>Number of children under 5 years of age</t>
-  </si>
-  <si>
-    <t>Number of elderly over 60 years of age</t>
-  </si>
-  <si>
     <t>Total Number of People Living with Disability</t>
   </si>
   <si>
-    <t>Number of people living with disability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% of Elderly </t>
+    <t>research_question</t>
+  </si>
+  <si>
+    <t>% of population with foregone health care needs</t>
+  </si>
+  <si>
+    <t>To estimate the incidence of infectious disease in the population</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>To estimate the extent which population is unable to access health services</t>
+  </si>
+  <si>
+    <t>% of population by self-reported barriers to health care</t>
+  </si>
+  <si>
+    <t>Vulnerability Characteristics</t>
+  </si>
+  <si>
+    <t>To understand the level of vulnerabilities of the target population</t>
+  </si>
+  <si>
+    <t>Household Dependency Ratio</t>
+  </si>
+  <si>
+    <t>Age Category, 5-year bins (%)</t>
+  </si>
+  <si>
+    <t>Age Category, 6-month bins  (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Elderly in the Population (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Women of Reproductive Age in the Population (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-2 Years of Age (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-5 Years of Age (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households with Individuals Living with Disability (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Residency Status (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Displaced Households, by Date of Arrival  (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Female Headed Households (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households, by Marital Status of Head of Household (%)</t>
+  </si>
+  <si>
+    <t>Disease Incidence</t>
+  </si>
+  <si>
+    <t>Proportion of population with health needs in the past two weeks (%)</t>
+  </si>
+  <si>
+    <t>Change of incidence of diarrhoeal disease in past four weeks (%)</t>
+  </si>
+  <si>
+    <t>Change of incidence of infectious disease in past four weeks (%)</t>
+  </si>
+  <si>
+    <t>Incidence of diarrhoeal disease in past four weeks (cases per 1000 per week)</t>
+  </si>
+  <si>
+    <t>Incidence of infectious disease in past four weeks (cases per 1000 per week)</t>
+  </si>
+  <si>
+    <t>To estimate the level of mortality in the target population</t>
+  </si>
+  <si>
+    <t>Crude Mortality Rate (deaths per 10,000 per day)</t>
+  </si>
+  <si>
+    <t>Under-5 Mortality Rate (deaths per 10,000 per day)</t>
+  </si>
+  <si>
+    <t>Nutritional Status</t>
+  </si>
+  <si>
+    <t>To estimate the level of acute malnutrition in the population</t>
+  </si>
+  <si>
+    <t>Number of children with Nutritional Oedema (#)</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
+  </si>
+  <si>
+    <t>Moderate Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
+  </si>
+  <si>
+    <t>Severe Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
+  </si>
+  <si>
+    <t>Global Acute Malnutrition by MUAC for Pregnant and Lactating Women (%)</t>
+  </si>
+  <si>
+    <t>FoodConsumption</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>WaterConsumption</t>
+  </si>
+  <si>
+    <t>ExposureDisease</t>
+  </si>
+  <si>
+    <t>HHFoodSecurity</t>
+  </si>
+  <si>
+    <t>HHConsumption</t>
+  </si>
+  <si>
+    <t>Availability</t>
+  </si>
+  <si>
+    <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Utilization</t>
+  </si>
+  <si>
+    <t>Stability</t>
+  </si>
+  <si>
+    <t>ReproductiveNumber</t>
+  </si>
+  <si>
+    <t>Hygiene</t>
+  </si>
+  <si>
+    <t>Livelihoods</t>
+  </si>
+  <si>
+    <t>Income</t>
+  </si>
+  <si>
+    <t>Assets</t>
+  </si>
+  <si>
+    <t>ProtectionElements</t>
+  </si>
+  <si>
+    <t>ProtectionVectors</t>
+  </si>
+  <si>
+    <t>Functionality</t>
+  </si>
+  <si>
+    <t>EnvironmentalHygiene</t>
+  </si>
+  <si>
+    <t>ShocksHazards</t>
+  </si>
+  <si>
+    <t>GovPolicyInstitution</t>
+  </si>
+  <si>
+    <t>CultureSocialNorms</t>
+  </si>
+  <si>
+    <t>Macroeconomy</t>
+  </si>
+  <si>
+    <t>Proportion of Displaced Households, by Date of Departure (%)</t>
+  </si>
+  <si>
+    <t>Migration</t>
+  </si>
+  <si>
+    <t>Population Movement</t>
+  </si>
+  <si>
+    <t>Vulnerability</t>
+  </si>
+  <si>
+    <t>In-Migration Rate</t>
+  </si>
+  <si>
+    <t>Out-Migration Rate</t>
+  </si>
+  <si>
+    <t>To understand the population movements for the target population</t>
+  </si>
+  <si>
+    <t>Severe Acute Malnutrition by MUAC for Pregnant and Lactating Women (%)</t>
+  </si>
+  <si>
+    <t>To estimate the proportion of the population with health care needs</t>
+  </si>
+  <si>
+    <t>Proportion of individuals with health needs by location healthcare sought</t>
+  </si>
+  <si>
+    <t>Proportion of individuals with health needs by alternative locations healthcare sought</t>
+  </si>
+  <si>
+    <t>Proportion of individuals 5 years or older ever received oral cholera vaccination</t>
+  </si>
+  <si>
+    <t>Proportion of individuals 6-59 months ever received measles vaccination</t>
+  </si>
+  <si>
+    <t>Proportion of individuals 6-59 months received Vitamin A supplementation in the previous 6 months</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Time to Access Nearest Functional Health Facilty in Minutes (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Reported Barriers to Health Care, by type of barrier (%)</t>
   </si>
 </sst>
 </file>
@@ -947,32 +1133,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}">
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="4" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
     <col min="5" max="5" width="47.85546875" customWidth="1"/>
     <col min="6" max="6" width="55.42578125" customWidth="1"/>
-    <col min="7" max="7" width="34.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.42578125" customWidth="1"/>
+    <col min="9" max="9" width="54" customWidth="1"/>
     <col min="10" max="10" width="26.42578125" customWidth="1"/>
-    <col min="11" max="12" width="17.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="13" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>64</v>
+        <v>145</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D1" t="s">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -981,39 +1169,42 @@
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" t="s">
         <v>135</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" t="s">
         <v>134</v>
       </c>
-      <c r="J1" t="s">
-        <v>138</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N1" t="s">
         <v>136</v>
       </c>
-      <c r="L1" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>65</v>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>110</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2">
-        <v>110</v>
+      <c r="D2" t="s">
+        <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>3</v>
@@ -1022,39 +1213,36 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H2">
         <v>11001</v>
       </c>
       <c r="I2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2" t="s">
         <v>143</v>
       </c>
-      <c r="J2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K2" t="s">
-        <v>150</v>
-      </c>
       <c r="L2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>65</v>
+        <v>144</v>
+      </c>
+      <c r="N2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>110</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="D3">
-        <v>110</v>
+      <c r="D3" t="s">
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>3</v>
@@ -1063,27 +1251,27 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H3">
         <v>11002</v>
       </c>
       <c r="I3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>65</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
       </c>
-      <c r="D4">
-        <v>110</v>
+      <c r="D4" t="s">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -1092,27 +1280,27 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H4">
         <v>11003</v>
       </c>
       <c r="I4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>65</v>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>110</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
       </c>
-      <c r="D5">
-        <v>110</v>
+      <c r="D5" t="s">
+        <v>0</v>
       </c>
       <c r="E5" t="s">
         <v>3</v>
@@ -1121,27 +1309,27 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H5">
         <v>11004</v>
       </c>
       <c r="I5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>65</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="D6">
-        <v>110</v>
+      <c r="D6" t="s">
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
@@ -1150,27 +1338,27 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H6">
         <v>11005</v>
       </c>
       <c r="I6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>65</v>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>110</v>
       </c>
       <c r="B7" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
       </c>
-      <c r="D7">
-        <v>110</v>
+      <c r="D7" t="s">
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
@@ -1179,27 +1367,27 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H7">
         <v>11006</v>
       </c>
       <c r="I7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>65</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>110</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8">
-        <v>110</v>
+      <c r="D8" t="s">
+        <v>0</v>
       </c>
       <c r="E8" t="s">
         <v>3</v>
@@ -1208,908 +1396,2354 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H8">
         <v>11007</v>
       </c>
       <c r="I8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>65</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>120</v>
+      <c r="D9" t="s">
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>158</v>
+        <v>5</v>
       </c>
       <c r="G9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H9">
-        <v>12001</v>
+        <v>11008</v>
       </c>
       <c r="I9" t="s">
-        <v>153</v>
-      </c>
-      <c r="J9" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>65</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>110</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10">
+        <v>11009</v>
+      </c>
+      <c r="I10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>120</v>
       </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" t="s">
-        <v>142</v>
-      </c>
-      <c r="H10">
-        <v>12002</v>
-      </c>
-      <c r="I10" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
       <c r="B11" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
       </c>
-      <c r="D11">
-        <v>120</v>
+      <c r="D11" t="s">
+        <v>4</v>
       </c>
       <c r="E11" t="s">
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H11">
-        <v>12003</v>
+        <v>12001</v>
       </c>
       <c r="I11" t="s">
-        <v>159</v>
-      </c>
-      <c r="J11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>65</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>120</v>
       </c>
       <c r="B12" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
         <v>0</v>
       </c>
-      <c r="D12">
-        <v>120</v>
+      <c r="D12" t="s">
+        <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H12">
-        <v>12004</v>
+        <v>12002</v>
       </c>
       <c r="I12" t="s">
-        <v>156</v>
-      </c>
-      <c r="J12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>65</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>120</v>
       </c>
       <c r="B13" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>0</v>
       </c>
-      <c r="D13">
-        <v>120</v>
+      <c r="D13" t="s">
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H13">
-        <v>12005</v>
+        <v>12003</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
-      </c>
-      <c r="J13" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>65</v>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>120</v>
       </c>
       <c r="B14" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>0</v>
       </c>
-      <c r="D14">
-        <v>120</v>
+      <c r="D14" t="s">
+        <v>4</v>
       </c>
       <c r="E14" t="s">
         <v>4</v>
       </c>
       <c r="F14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14">
+        <v>12004</v>
+      </c>
+      <c r="I14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>120</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15">
+        <v>12005</v>
+      </c>
+      <c r="I15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>120</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16">
+        <v>12006</v>
+      </c>
+      <c r="I16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17">
+        <v>13001</v>
+      </c>
+      <c r="I17" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" t="s">
+        <v>159</v>
+      </c>
+      <c r="F18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18">
+        <v>13002</v>
+      </c>
+      <c r="I18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>130</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19">
+        <v>13003</v>
+      </c>
+      <c r="I19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>130</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" t="s">
+        <v>159</v>
+      </c>
+      <c r="F20" t="s">
+        <v>160</v>
+      </c>
+      <c r="G20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20">
+        <v>13004</v>
+      </c>
+      <c r="I20" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>130</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" t="s">
+        <v>159</v>
+      </c>
+      <c r="F21" t="s">
+        <v>160</v>
+      </c>
+      <c r="G21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21">
+        <v>13005</v>
+      </c>
+      <c r="I21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" t="s">
+        <v>139</v>
+      </c>
+      <c r="H22">
+        <v>13006</v>
+      </c>
+      <c r="I22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23">
+        <v>13007</v>
+      </c>
+      <c r="I23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
+        <v>214</v>
+      </c>
+      <c r="E24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F24" t="s">
+        <v>219</v>
+      </c>
+      <c r="G24" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24">
+        <v>14001</v>
+      </c>
+      <c r="I24" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E25" t="s">
+        <v>215</v>
+      </c>
+      <c r="F25" t="s">
+        <v>219</v>
+      </c>
+      <c r="G25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25">
+        <v>14002</v>
+      </c>
+      <c r="I25" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>221</v>
+      </c>
+      <c r="G26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26">
+        <v>15001</v>
+      </c>
+      <c r="I26" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>150</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H27">
+        <v>15002</v>
+      </c>
+      <c r="I27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>150</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>179</v>
+      </c>
+      <c r="G28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H28">
+        <v>15003</v>
+      </c>
+      <c r="I28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>160</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>173</v>
+      </c>
+      <c r="F29" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" t="s">
+        <v>156</v>
+      </c>
+      <c r="H29">
+        <v>16001</v>
+      </c>
+      <c r="I29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>160</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>173</v>
+      </c>
+      <c r="F30" t="s">
+        <v>155</v>
+      </c>
+      <c r="G30" t="s">
+        <v>156</v>
+      </c>
+      <c r="H30">
+        <v>16002</v>
+      </c>
+      <c r="I30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>160</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>173</v>
+      </c>
+      <c r="F31" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31">
+        <v>16003</v>
+      </c>
+      <c r="I31" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>160</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" t="s">
+        <v>155</v>
+      </c>
+      <c r="G32" t="s">
+        <v>156</v>
+      </c>
+      <c r="H32">
+        <v>16004</v>
+      </c>
+      <c r="I32" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>103</v>
+      </c>
+      <c r="D33" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" t="s">
+        <v>139</v>
+      </c>
+      <c r="H33">
+        <v>17001</v>
+      </c>
+      <c r="I33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>170</v>
+      </c>
+      <c r="B34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F34" t="s">
+        <v>183</v>
+      </c>
+      <c r="G34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34">
+        <v>17002</v>
+      </c>
+      <c r="I34" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>170</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35">
+        <v>17003</v>
+      </c>
+      <c r="I35" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>170</v>
+      </c>
+      <c r="B36" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" t="s">
+        <v>183</v>
+      </c>
+      <c r="G36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36">
+        <v>17004</v>
+      </c>
+      <c r="I36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" t="s">
+        <v>183</v>
+      </c>
+      <c r="G37" t="s">
+        <v>139</v>
+      </c>
+      <c r="H37">
+        <v>17005</v>
+      </c>
+      <c r="I37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>170</v>
+      </c>
+      <c r="B38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" t="s">
+        <v>183</v>
+      </c>
+      <c r="G38" t="s">
+        <v>139</v>
+      </c>
+      <c r="H38">
+        <v>17006</v>
+      </c>
+      <c r="I38" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>180</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>180</v>
+      </c>
+      <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>190</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>190</v>
+      </c>
+      <c r="B42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C42" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>200</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>200</v>
+      </c>
+      <c r="B44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>210</v>
+      </c>
+      <c r="B45" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" t="s">
+        <v>194</v>
+      </c>
+      <c r="D45" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>220</v>
+      </c>
+      <c r="B46" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" t="s">
+        <v>194</v>
+      </c>
+      <c r="D46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>230</v>
+      </c>
+      <c r="B47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" t="s">
+        <v>194</v>
+      </c>
+      <c r="D47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>240</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" t="s">
+        <v>194</v>
+      </c>
+      <c r="D48" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>250</v>
+      </c>
+      <c r="B49" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" t="s">
+        <v>194</v>
+      </c>
+      <c r="D49" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>260</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" t="s">
+        <v>75</v>
+      </c>
+      <c r="D50" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>270</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>280</v>
+      </c>
+      <c r="B52" t="s">
+        <v>67</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>290</v>
+      </c>
+      <c r="B53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>300</v>
+      </c>
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>310</v>
+      </c>
+      <c r="B55" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>320</v>
+      </c>
+      <c r="B56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>330</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D57" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>340</v>
+      </c>
+      <c r="B58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>350</v>
+      </c>
+      <c r="B59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>360</v>
+      </c>
+      <c r="B60" t="s">
+        <v>67</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>370</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>380</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s">
+        <v>202</v>
+      </c>
+      <c r="D62" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>390</v>
+      </c>
+      <c r="B63" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>400</v>
+      </c>
+      <c r="B64" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>410</v>
+      </c>
+      <c r="B65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>420</v>
+      </c>
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>430</v>
+      </c>
+      <c r="B67" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" t="s">
+        <v>93</v>
+      </c>
+      <c r="D67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>440</v>
+      </c>
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>450</v>
+      </c>
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C69" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>460</v>
+      </c>
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" t="s">
+        <v>71</v>
+      </c>
+      <c r="D70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>470</v>
+      </c>
+      <c r="B71" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>71</v>
+      </c>
+      <c r="D71" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>480</v>
+      </c>
+      <c r="B72" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" t="s">
+        <v>71</v>
+      </c>
+      <c r="D72" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>490</v>
+      </c>
+      <c r="B73" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" t="s">
+        <v>71</v>
+      </c>
+      <c r="D73" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>500</v>
+      </c>
+      <c r="B74" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" t="s">
+        <v>71</v>
+      </c>
+      <c r="D74" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>510</v>
+      </c>
+      <c r="B75" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>520</v>
+      </c>
+      <c r="B76" t="s">
+        <v>64</v>
+      </c>
+      <c r="C76" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" t="s">
+        <v>197</v>
+      </c>
+      <c r="H76">
+        <v>52001</v>
+      </c>
+      <c r="I76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>520</v>
+      </c>
+      <c r="B77" t="s">
+        <v>64</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" t="s">
+        <v>197</v>
+      </c>
+      <c r="H77">
+        <v>52002</v>
+      </c>
+      <c r="I77" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>530</v>
+      </c>
+      <c r="B78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>540</v>
+      </c>
+      <c r="B79" t="s">
+        <v>64</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" t="s">
+        <v>198</v>
+      </c>
+      <c r="H79">
+        <v>54001</v>
+      </c>
+      <c r="I79" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>540</v>
+      </c>
+      <c r="B80" t="s">
+        <v>64</v>
+      </c>
+      <c r="C80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" t="s">
+        <v>198</v>
+      </c>
+      <c r="H80">
+        <v>54002</v>
+      </c>
+      <c r="I80" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>550</v>
+      </c>
+      <c r="B84" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" t="s">
+        <v>70</v>
+      </c>
+      <c r="D84" t="s">
+        <v>105</v>
+      </c>
+      <c r="H84">
+        <v>55001</v>
+      </c>
+      <c r="I84" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>550</v>
+      </c>
+      <c r="B85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D85" t="s">
+        <v>105</v>
+      </c>
+      <c r="H85">
+        <v>55002</v>
+      </c>
+      <c r="I85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>550</v>
+      </c>
+      <c r="B86" t="s">
+        <v>64</v>
+      </c>
+      <c r="C86" t="s">
+        <v>70</v>
+      </c>
+      <c r="D86" t="s">
+        <v>105</v>
+      </c>
+      <c r="H86">
+        <v>55003</v>
+      </c>
+      <c r="I86" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>560</v>
+      </c>
+      <c r="B88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C88" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>570</v>
+      </c>
+      <c r="B89" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" t="s">
+        <v>79</v>
+      </c>
+      <c r="D89" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>580</v>
+      </c>
+      <c r="B90" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>590</v>
+      </c>
+      <c r="B91" t="s">
+        <v>210</v>
+      </c>
+      <c r="C91" t="s">
+        <v>210</v>
+      </c>
+      <c r="D91" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>600</v>
+      </c>
+      <c r="B92" t="s">
+        <v>211</v>
+      </c>
+      <c r="C92" t="s">
+        <v>211</v>
+      </c>
+      <c r="D92" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>610</v>
+      </c>
+      <c r="B93" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" t="s">
+        <v>212</v>
+      </c>
+      <c r="D93" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>64</v>
+      </c>
+      <c r="C119" t="s">
+        <v>70</v>
+      </c>
+      <c r="D119" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s">
+        <v>157</v>
+      </c>
+      <c r="G119" t="s">
+        <v>139</v>
+      </c>
+      <c r="H119">
+        <v>14001</v>
+      </c>
+      <c r="I119" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>64</v>
+      </c>
+      <c r="C120" t="s">
+        <v>70</v>
+      </c>
+      <c r="D120" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" t="s">
+        <v>8</v>
+      </c>
+      <c r="G120" t="s">
+        <v>139</v>
+      </c>
+      <c r="H120">
+        <v>14002</v>
+      </c>
+      <c r="I120" t="s">
         <v>158</v>
       </c>
-      <c r="G14" t="s">
-        <v>142</v>
-      </c>
-      <c r="H14">
-        <v>12006</v>
-      </c>
-      <c r="I14" t="s">
-        <v>164</v>
-      </c>
-      <c r="J14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121" t="s">
+        <v>70</v>
+      </c>
+      <c r="D121" t="s">
+        <v>21</v>
+      </c>
+      <c r="E121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>65</v>
+      </c>
+      <c r="C125" t="s">
+        <v>73</v>
+      </c>
+      <c r="D125" t="s">
+        <v>27</v>
+      </c>
+      <c r="E125" t="s">
+        <v>12</v>
+      </c>
+      <c r="F125" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" t="s">
+        <v>73</v>
+      </c>
+      <c r="D126" t="s">
+        <v>28</v>
+      </c>
+      <c r="E126" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>64</v>
+      </c>
+      <c r="C127" t="s">
+        <v>70</v>
+      </c>
+      <c r="D127" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
         <v>66</v>
       </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="C128" t="s">
+        <v>71</v>
+      </c>
+      <c r="D128" t="s">
+        <v>15</v>
+      </c>
+      <c r="E128" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
         <v>66</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C129" t="s">
+        <v>71</v>
+      </c>
+      <c r="D129" t="s">
+        <v>22</v>
+      </c>
+      <c r="E129" t="s">
+        <v>24</v>
+      </c>
+      <c r="F129" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>65</v>
+      </c>
+      <c r="C130" t="s">
+        <v>73</v>
+      </c>
+      <c r="D130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" t="s">
+        <v>39</v>
+      </c>
+      <c r="F130" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>65</v>
+      </c>
+      <c r="C131" t="s">
+        <v>73</v>
+      </c>
+      <c r="D131" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" t="s">
+        <v>38</v>
+      </c>
+      <c r="F131" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>65</v>
+      </c>
+      <c r="C132" t="s">
+        <v>73</v>
+      </c>
+      <c r="D132" t="s">
+        <v>28</v>
+      </c>
+      <c r="E132" t="s">
+        <v>49</v>
+      </c>
+      <c r="F132" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>65</v>
+      </c>
+      <c r="C133" t="s">
+        <v>73</v>
+      </c>
+      <c r="D133" t="s">
+        <v>51</v>
+      </c>
+      <c r="E133" t="s">
+        <v>128</v>
+      </c>
+      <c r="F133" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>65</v>
+      </c>
+      <c r="C134" t="s">
+        <v>73</v>
+      </c>
+      <c r="D134" t="s">
+        <v>51</v>
+      </c>
+      <c r="E134" t="s">
+        <v>50</v>
+      </c>
+      <c r="F134" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>65</v>
+      </c>
+      <c r="C135" t="s">
+        <v>73</v>
+      </c>
+      <c r="D135" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s">
+        <v>52</v>
+      </c>
+      <c r="F135" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>67</v>
+      </c>
+      <c r="C136" t="s">
+        <v>75</v>
+      </c>
+      <c r="D136" t="s">
+        <v>53</v>
+      </c>
+      <c r="E136" t="s">
+        <v>54</v>
+      </c>
+      <c r="F136" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>67</v>
+      </c>
+      <c r="C137" t="s">
+        <v>75</v>
+      </c>
+      <c r="D137" t="s">
+        <v>53</v>
+      </c>
+      <c r="E137" t="s">
+        <v>55</v>
+      </c>
+      <c r="F137" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>67</v>
+      </c>
+      <c r="C138" t="s">
+        <v>75</v>
+      </c>
+      <c r="D138" t="s">
+        <v>57</v>
+      </c>
+      <c r="E138" t="s">
+        <v>58</v>
+      </c>
+      <c r="F138" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>67</v>
+      </c>
+      <c r="C139" t="s">
+        <v>75</v>
+      </c>
+      <c r="D139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" t="s">
+        <v>59</v>
+      </c>
+      <c r="F139" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>67</v>
+      </c>
+      <c r="C140" t="s">
+        <v>75</v>
+      </c>
+      <c r="D140" t="s">
+        <v>76</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G140" s="1"/>
+    </row>
+    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>67</v>
+      </c>
+      <c r="C141" t="s">
+        <v>75</v>
+      </c>
+      <c r="D141" t="s">
+        <v>76</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>67</v>
+      </c>
+      <c r="C142" t="s">
+        <v>75</v>
+      </c>
+      <c r="D142" t="s">
+        <v>77</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G142" s="1"/>
+    </row>
+    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>67</v>
+      </c>
+      <c r="C143" t="s">
+        <v>79</v>
+      </c>
+      <c r="D143" t="s">
+        <v>78</v>
+      </c>
+      <c r="E143" t="s">
+        <v>80</v>
+      </c>
+      <c r="F143" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>67</v>
+      </c>
+      <c r="C144" t="s">
+        <v>79</v>
+      </c>
+      <c r="D144" t="s">
+        <v>81</v>
+      </c>
+      <c r="E144" t="s">
+        <v>82</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G144" s="2"/>
+    </row>
+    <row r="145" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>63</v>
+      </c>
+      <c r="C145" t="s">
+        <v>87</v>
+      </c>
+      <c r="D145" t="s">
+        <v>88</v>
+      </c>
+      <c r="E145" t="s">
+        <v>89</v>
+      </c>
+      <c r="F145" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>63</v>
+      </c>
+      <c r="C146" t="s">
         <v>72</v>
       </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D146" t="s">
+        <v>90</v>
+      </c>
+      <c r="E146" t="s">
+        <v>125</v>
+      </c>
+      <c r="F146" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>63</v>
+      </c>
+      <c r="C147" t="s">
+        <v>72</v>
+      </c>
+      <c r="D147" t="s">
+        <v>90</v>
+      </c>
+      <c r="E147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F147" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>63</v>
+      </c>
+      <c r="C148" t="s">
+        <v>72</v>
+      </c>
+      <c r="D148" t="s">
+        <v>91</v>
+      </c>
+      <c r="E148" t="s">
+        <v>92</v>
+      </c>
+      <c r="F148" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
         <v>67</v>
       </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="C149" t="s">
+        <v>93</v>
+      </c>
+      <c r="D149" t="s">
+        <v>74</v>
+      </c>
+      <c r="E149" t="s">
+        <v>94</v>
+      </c>
+      <c r="F149" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
         <v>67</v>
       </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="C150" t="s">
+        <v>93</v>
+      </c>
+      <c r="D150" t="s">
+        <v>74</v>
+      </c>
+      <c r="E150" t="s">
+        <v>97</v>
+      </c>
+      <c r="F150" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>67</v>
+      </c>
+      <c r="C151" t="s">
+        <v>79</v>
+      </c>
+      <c r="D151" t="s">
+        <v>78</v>
+      </c>
+      <c r="E151" t="s">
+        <v>100</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G151" s="2"/>
+    </row>
+    <row r="152" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>67</v>
+      </c>
+      <c r="C152" t="s">
+        <v>79</v>
+      </c>
+      <c r="D152" t="s">
+        <v>78</v>
+      </c>
+      <c r="E152" t="s">
+        <v>101</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G152" s="2"/>
+    </row>
+    <row r="153" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
         <v>66</v>
       </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="C153" t="s">
+        <v>103</v>
+      </c>
+      <c r="D153" t="s">
+        <v>103</v>
+      </c>
+      <c r="E153" t="s">
+        <v>104</v>
+      </c>
+      <c r="F153" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
         <v>66</v>
       </c>
-      <c r="B21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F26" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" t="s">
-        <v>52</v>
-      </c>
-      <c r="F27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>69</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="F34" s="1" t="s">
+      <c r="C154" t="s">
+        <v>103</v>
+      </c>
+      <c r="D154" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>64</v>
+      </c>
+      <c r="C155" t="s">
+        <v>70</v>
+      </c>
+      <c r="D155" t="s">
+        <v>105</v>
+      </c>
+      <c r="E155" t="s">
+        <v>106</v>
+      </c>
+      <c r="F155" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>64</v>
+      </c>
+      <c r="C156" t="s">
+        <v>70</v>
+      </c>
+      <c r="D156" t="s">
+        <v>105</v>
+      </c>
+      <c r="E156" t="s">
+        <v>107</v>
+      </c>
+      <c r="F156" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>64</v>
+      </c>
+      <c r="C157" t="s">
+        <v>70</v>
+      </c>
+      <c r="D157" t="s">
+        <v>105</v>
+      </c>
+      <c r="E157" t="s">
+        <v>108</v>
+      </c>
+      <c r="F157" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="158" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>64</v>
+      </c>
+      <c r="C158" t="s">
+        <v>85</v>
+      </c>
+      <c r="D158" t="s">
+        <v>85</v>
+      </c>
+      <c r="E158" t="s">
+        <v>109</v>
+      </c>
+      <c r="F158" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="159" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159" t="s">
+        <v>86</v>
+      </c>
+      <c r="D159" t="s">
+        <v>83</v>
+      </c>
+      <c r="E159" t="s">
+        <v>122</v>
+      </c>
+      <c r="F159" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="160" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>84</v>
+      </c>
+      <c r="C160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D160" t="s">
+        <v>83</v>
+      </c>
+      <c r="E160" t="s">
+        <v>123</v>
+      </c>
+      <c r="F160" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>64</v>
+      </c>
+      <c r="C161" t="s">
+        <v>86</v>
+      </c>
+      <c r="D161" t="s">
         <v>118</v>
       </c>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="E161" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F161" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>69</v>
-      </c>
-      <c r="B36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
-      <c r="E36" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>69</v>
-      </c>
-      <c r="B37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" t="s">
-        <v>83</v>
-      </c>
-      <c r="E37" t="s">
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E38" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="C162" t="s">
+        <v>86</v>
+      </c>
+      <c r="D162" t="s">
+        <v>110</v>
+      </c>
+      <c r="E162" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" t="s">
-        <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" t="s">
-        <v>130</v>
-      </c>
-      <c r="F40" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C41" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" t="s">
-        <v>96</v>
-      </c>
-      <c r="F42" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>69</v>
-      </c>
-      <c r="B43" t="s">
-        <v>95</v>
-      </c>
-      <c r="C43" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
-      <c r="E44" t="s">
-        <v>102</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>69</v>
-      </c>
-      <c r="B45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" t="s">
-        <v>103</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" t="s">
-        <v>105</v>
-      </c>
-      <c r="C46" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" t="s">
-        <v>107</v>
-      </c>
-      <c r="F46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>68</v>
-      </c>
-      <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="E47" t="s">
-        <v>106</v>
-      </c>
-      <c r="F47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" t="s">
-        <v>109</v>
-      </c>
-      <c r="F48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E49" t="s">
-        <v>110</v>
-      </c>
-      <c r="F49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" t="s">
-        <v>108</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F162" t="s">
         <v>111</v>
-      </c>
-      <c r="F50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>66</v>
-      </c>
-      <c r="B51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C51" t="s">
-        <v>87</v>
-      </c>
-      <c r="E51" t="s">
-        <v>112</v>
-      </c>
-      <c r="F51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>86</v>
-      </c>
-      <c r="B52" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" t="s">
-        <v>125</v>
-      </c>
-      <c r="F52" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>85</v>
-      </c>
-      <c r="E53" t="s">
-        <v>126</v>
-      </c>
-      <c r="F53" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>66</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" t="s">
-        <v>123</v>
-      </c>
-      <c r="F54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>113</v>
-      </c>
-      <c r="E55" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/resources/reference.xlsx
+++ b/resources/reference.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63845B0C-181F-442F-A798-8259E2C60691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712F93F2-4C37-4E53-BE64-16EEEBC8EB9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A81D9A7-8734-4191-8BBE-89A5AF7A65A9}"/>
   </bookViews>
   <sheets>
     <sheet name="objectives" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="439">
   <si>
     <t>Demographics</t>
   </si>
@@ -479,42 +479,12 @@
     <t>Sex Ratio</t>
   </si>
   <si>
-    <t>Average Household Size</t>
-  </si>
-  <si>
-    <t>Mean Age (years)</t>
-  </si>
-  <si>
-    <t># of males</t>
-  </si>
-  <si>
-    <t># of females</t>
-  </si>
-  <si>
     <t>objective_code</t>
   </si>
   <si>
-    <t>Total Population Size</t>
-  </si>
-  <si>
-    <t>Total Number of Pregnant and Lactating Women</t>
-  </si>
-  <si>
-    <t>Total Number of Children Under-5</t>
-  </si>
-  <si>
-    <t>Total Number of Elderly</t>
-  </si>
-  <si>
     <t>To estimate the total number of individuals in the population for assessed sites for services</t>
   </si>
   <si>
-    <t>Total Number of Children Under-2</t>
-  </si>
-  <si>
-    <t>Total Number of People Living with Disability</t>
-  </si>
-  <si>
     <t>research_question</t>
   </si>
   <si>
@@ -539,9 +509,6 @@
     <t>To understand the level of vulnerabilities of the target population</t>
   </si>
   <si>
-    <t>Household Dependency Ratio</t>
-  </si>
-  <si>
     <t>Age Category, 5-year bins (%)</t>
   </si>
   <si>
@@ -590,9 +557,6 @@
     <t>Incidence of diarrhoeal disease in past four weeks (cases per 1000 per week)</t>
   </si>
   <si>
-    <t>Incidence of infectious disease in past four weeks (cases per 1000 per week)</t>
-  </si>
-  <si>
     <t>To estimate the level of mortality in the target population</t>
   </si>
   <si>
@@ -608,18 +572,9 @@
     <t>To estimate the level of acute malnutrition in the population</t>
   </si>
   <si>
-    <t>Number of children with Nutritional Oedema (#)</t>
-  </si>
-  <si>
     <t>Global Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
   </si>
   <si>
-    <t>Moderate Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
-  </si>
-  <si>
-    <t>Severe Acute Malnutrition by MUAC for Children 6-59 months (%)</t>
-  </si>
-  <si>
     <t>Global Acute Malnutrition by MUAC for Pregnant and Lactating Women (%)</t>
   </si>
   <si>
@@ -707,18 +662,9 @@
     <t>Vulnerability</t>
   </si>
   <si>
-    <t>In-Migration Rate</t>
-  </si>
-  <si>
-    <t>Out-Migration Rate</t>
-  </si>
-  <si>
     <t>To understand the population movements for the target population</t>
   </si>
   <si>
-    <t>Severe Acute Malnutrition by MUAC for Pregnant and Lactating Women (%)</t>
-  </si>
-  <si>
     <t>To estimate the proportion of the population with health care needs</t>
   </si>
   <si>
@@ -741,6 +687,690 @@
   </si>
   <si>
     <t>Proportion of Households by Reported Barriers to Health Care, by type of barrier (%)</t>
+  </si>
+  <si>
+    <t>HHConsumption - Quantity</t>
+  </si>
+  <si>
+    <t>HHConsumption - Quality</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Water Source for Food Preparation (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Barriers to Food Access (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Main Sources of Food (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Food Consumption Score (FCS) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Household Hunger Scale (HHS) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Reduced Coping Strategies Index (rCSI) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Household Dietary Diversity Score (HDDS) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Fuel Source for Food Preparation (%)</t>
+  </si>
+  <si>
+    <t>Average Number of Meals per Day (#)</t>
+  </si>
+  <si>
+    <t>Average Household Size (#)</t>
+  </si>
+  <si>
+    <t>Mean Age (years) (#)</t>
+  </si>
+  <si>
+    <t>Total Population Size (#)</t>
+  </si>
+  <si>
+    <t>Total Number of Pregnant and Lactating Women (#)</t>
+  </si>
+  <si>
+    <t>Total Number of Children Under-2 (#)</t>
+  </si>
+  <si>
+    <t>Total Number of Children Under-5 (#)</t>
+  </si>
+  <si>
+    <t>Total Number of Elderly (#)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Main Sources of Income (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Livelihoods Coping Strategies Index (LCSI) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households Registered/Received Food Assistance (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Barriers to Market Access (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Purchase Barriers (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Main Source of Water (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Alternative Sources of Water (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Usage of Main Water Source (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Usage of Alternative Water Source (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Time to Collect Water (minutes) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Water Treatment Method (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Water Interruption in Previous Two Weeks (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Water Container Ownership (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Soap Ownership (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Household Water Insecurity Experiences Scale (HWISE) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Mosquito Net Ownership (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Mosquito Net Utilization by Children (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Latrine Access (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households Sharing Latrines (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households with at least 3.5 Square Meters of Accomodation per Person (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Shelter Type (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Shelter Issues (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Cooking Issues in the Shelter (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Issues for Storing Food and Water (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Issues Sleeping in Shelter (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Lighting Issues (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Households by Hygiene Issues in the Shelter (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Acutely Malnourished Children Accessing Therapeutic Nutrition Services (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-2 by Caregiver Reported Barriers to Breastfeeding (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-2 by Caregiver Reported Barriers to Complementary Feeding (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-2 by Infant Young Child Feeding Practices in Emergencies (IYCF-E) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Children Under-2 by Early Childhood Food Insecurity Experience Scale (EC-FIESE) (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Acutely Malnourished Pregnant or Lactating Women Accessing Preventive Nutrition Services (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Deceased Individuals by Access to Healthcare in Two Weeks Prior to Death (%)</t>
+  </si>
+  <si>
+    <t>Proportion of Deceased Individuals by Healthcare Seeking Behaviour in Two Weeks Prior to Death (%)</t>
+  </si>
+  <si>
+    <t>Ratio of males to females in the population</t>
+  </si>
+  <si>
+    <t># of individuals all ages</t>
+  </si>
+  <si>
+    <t># of children under-5 years of age</t>
+  </si>
+  <si>
+    <t>Average number of household members at the time of the survey</t>
+  </si>
+  <si>
+    <t># of household members</t>
+  </si>
+  <si>
+    <t>The average age in years of all household members</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Proportion of individuals per 5-year age groupings from 0-100 years of age</t>
+  </si>
+  <si>
+    <t>Proportion of individuals per 6-month age groupings from 0-60 months</t>
+  </si>
+  <si>
+    <t>Food Consumption Quantity</t>
+  </si>
+  <si>
+    <t>Food Consumption Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To estimate the quantity of individual food consumption </t>
+  </si>
+  <si>
+    <t xml:space="preserve">To estimate the quantity of individual water consumption </t>
+  </si>
+  <si>
+    <t>To identify the likely risk of disease transmission</t>
+  </si>
+  <si>
+    <t>Disease Specific Characteristics</t>
+  </si>
+  <si>
+    <t>Water Consumption Quantity</t>
+  </si>
+  <si>
+    <t>Water Consumption Quality</t>
+  </si>
+  <si>
+    <t>Proportion of individuals older than 65 years out of all individuals in sampled households</t>
+  </si>
+  <si>
+    <t>Proportion of childern under 2 years of age out of all individuals in sampled households</t>
+  </si>
+  <si>
+    <t>Proportion of childern under 5 years of age out of all individuals in sampled households</t>
+  </si>
+  <si>
+    <t>Proportion of individuals who are pregnant or lactating a child under 6 months of age at the time of the survey in all sampled households</t>
+  </si>
+  <si>
+    <t># of individuals currently breastfeeding or breastfeeding a child under 6 months of age</t>
+  </si>
+  <si>
+    <t>Estimated total of individuals in assessed sites</t>
+  </si>
+  <si>
+    <t>Estimated total of pregnant and lactating women ages 15-49 years of age in assessed sites</t>
+  </si>
+  <si>
+    <t>Estimated total of children 0-23 months in assessed sites</t>
+  </si>
+  <si>
+    <t>Estimated total of children 0-59 months in assessed sites</t>
+  </si>
+  <si>
+    <t>Estimated total of individuals ages 65+ years in assessed sites</t>
+  </si>
+  <si>
+    <t>Proportion of households where at least one household member relied on someone else for daily activities, relid on assistive devices, or need information in sign language</t>
+  </si>
+  <si>
+    <t># of assessed households with at least one member who relied on someone else for daily activities, relid on assistive devices, or need information in sign language</t>
+  </si>
+  <si>
+    <t># of children 0-23 months in assessed households</t>
+  </si>
+  <si>
+    <t># of children 0-59 months in assessed households</t>
+  </si>
+  <si>
+    <t># of PLWs in assessed households</t>
+  </si>
+  <si>
+    <t># of individuals in assessed households</t>
+  </si>
+  <si>
+    <t>citation</t>
+  </si>
+  <si>
+    <t>https://www.un.org/esa/sustdev/natlinfo/indicators/methodology_sheets/demographics/dependency_ratio.pdf#:~:text=Name:%20Dependency%20Ratio.%20(b)%20Brief%20Definition:%20The,to%20the%20working%2Dage%20population%20(15%2D64%20years%20old).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ratio of children ages 0-14 years and elderly aged 65 years and older to working age individuals ages 15-64 years. </t>
+  </si>
+  <si>
+    <t># of individuals 0-14 years and 65+ years in assessed households</t>
+  </si>
+  <si>
+    <t># of individuals 15-64 years of age in assessed households</t>
+  </si>
+  <si>
+    <t>Dependency Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportion of households that self-reported their residency status as host community, internally displaced persons (IDP), IDP returnees, refugees, or refugee returnees. Technical definitions for these population groups should follow in country guidance. </t>
+  </si>
+  <si>
+    <t># of households with a reported residency status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportion of displaced households by month of arrival at their current location divided by all displaced households assessed. </t>
+  </si>
+  <si>
+    <t># of total assessed households</t>
+  </si>
+  <si>
+    <t># of household members in all assessed households</t>
+  </si>
+  <si>
+    <t># of individuals in age group from all assessed households</t>
+  </si>
+  <si>
+    <t># of individuals 65 years of older in all assessed households</t>
+  </si>
+  <si>
+    <t># of individuals 65+ years in assessed households</t>
+  </si>
+  <si>
+    <t># of males in assessed households</t>
+  </si>
+  <si>
+    <t># of females in assessed households</t>
+  </si>
+  <si>
+    <t># of children under-2 years of age in assessed households</t>
+  </si>
+  <si>
+    <t># of individuals all ages in assessed households</t>
+  </si>
+  <si>
+    <t># of individuals in all assessed households</t>
+  </si>
+  <si>
+    <t># of individuals from ages 0-60 months in all assessed households</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proportion of displaced households by month of departure from area of origin divided by all displaced households assessed. </t>
+  </si>
+  <si>
+    <t># of assessed displaced households by month of departure</t>
+  </si>
+  <si>
+    <t># of assessed displaced households by month of arrival</t>
+  </si>
+  <si>
+    <t>Proportion of assessed households with female heads of household</t>
+  </si>
+  <si>
+    <t># of assessed households with female head of household</t>
+  </si>
+  <si>
+    <t>Proportion of households by marital status of the head of household</t>
+  </si>
+  <si>
+    <t># of assessed households by marital status of head of household</t>
+  </si>
+  <si>
+    <t>Ratio of individuals who have joined assessed households per 1000 population per day</t>
+  </si>
+  <si>
+    <t>Ratio of individuals who have left assessed households per 1000 population per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># of individuals reported leaving households during the recall period </t>
+  </si>
+  <si>
+    <t xml:space="preserve"># of individuals reported joining households during the recall period </t>
+  </si>
+  <si>
+    <t># of person-days</t>
+  </si>
+  <si>
+    <t>In-Migration Rate (per 1000)</t>
+  </si>
+  <si>
+    <t>Out-Migration Rate (per 1000)</t>
+  </si>
+  <si>
+    <t>Proportion of individuals in assessed households reportedly having a health need in the two weeks prior to data collection</t>
+  </si>
+  <si>
+    <t>Ratio of deaths to person-time during the recall period per 10000 people per day</t>
+  </si>
+  <si>
+    <t># of deaths reported during recall period in assessed households</t>
+  </si>
+  <si>
+    <t># of individuals with health needs in last two weeks in assessed households</t>
+  </si>
+  <si>
+    <t># of person-days observed in assessed households</t>
+  </si>
+  <si>
+    <t>Ratio of under-5 year old deaths to under-5 year old person-time during the recall period per 10000 under-5 year olds per day</t>
+  </si>
+  <si>
+    <t># of cases of syndromic diseases in the past four weeks</t>
+  </si>
+  <si>
+    <t># of people in the population served by reporting health facilities</t>
+  </si>
+  <si>
+    <t>Number of cases of syndromic diseases (fever, diarrhoea, cough, etc.) reported by health care facilities in the population over a four week period of time</t>
+  </si>
+  <si>
+    <t>Four week incidence of syndromic disease (cases per 1000)</t>
+  </si>
+  <si>
+    <t>Percent change in incidence of syndromic cases over a four week period of time</t>
+  </si>
+  <si>
+    <t># of cases per 1000 people per week four weeks (point 1)</t>
+  </si>
+  <si>
+    <t># of cases per 1000 people per week four weeks (point 2)</t>
+  </si>
+  <si>
+    <t>Number of cases of diarrhoeal diseases reported by health care facilities in the population over a four week period of time</t>
+  </si>
+  <si>
+    <t>Percent change in incidence of diarrhoeal cases over a four week period of time</t>
+  </si>
+  <si>
+    <t># of diarrhoeal disease cases per 1000 people per week four weeks (point 1)</t>
+  </si>
+  <si>
+    <t># of cases of diarrhoeal diseases in the past four weeks</t>
+  </si>
+  <si>
+    <t># of diarrhoeal cases per 1000 people per week four weeks (point 2)</t>
+  </si>
+  <si>
+    <t># of children 6-59 months of age with MUAC &lt; 125mm and/or presence of bilateral pitting oedema</t>
+  </si>
+  <si>
+    <t># of PLWs with MUAC &lt; 230mm and/or presence of bilateral pitting oedema</t>
+  </si>
+  <si>
+    <t># of children 6-59 months measured</t>
+  </si>
+  <si>
+    <t># of PLWs measured</t>
+  </si>
+  <si>
+    <t>Prevalence of children 6-59 months with a mid upper arm circumference measurement of less than 125mm and/or presence of bilateral pitting oedema</t>
+  </si>
+  <si>
+    <t>Prevalence of PLWs with a mid upper arm circumference measurement of less than 230mm</t>
+  </si>
+  <si>
+    <t>Proportion of children under-2 years of age by ECFIES severity classification</t>
+  </si>
+  <si>
+    <t># of children by ECFIES severity classification</t>
+  </si>
+  <si>
+    <t>Liters per person per day (rate)</t>
+  </si>
+  <si>
+    <t>Proportion of children under-2 years of age by IYCF-E practices</t>
+  </si>
+  <si>
+    <t>To estimate the quality of individual food consumption</t>
+  </si>
+  <si>
+    <t># of children by food groups consumed the previous day</t>
+  </si>
+  <si>
+    <t>Number of liters consumed by all members from the household on average per day</t>
+  </si>
+  <si>
+    <t># of liters per day</t>
+  </si>
+  <si>
+    <t># of individuals in assessed household</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the level of hygienic practices in the population </t>
+  </si>
+  <si>
+    <t>HH Consumption</t>
+  </si>
+  <si>
+    <t>To understand the quantity of food consumption by households as a whole</t>
+  </si>
+  <si>
+    <t>To understand the quality of food consumption by households as a whole</t>
+  </si>
+  <si>
+    <t>HH Food Availability</t>
+  </si>
+  <si>
+    <t>HH Food Accessibility</t>
+  </si>
+  <si>
+    <t>HH Food Utilization</t>
+  </si>
+  <si>
+    <t>HH Food Stability</t>
+  </si>
+  <si>
+    <t>To understand the level of access and barriers to food in the target population</t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to food utilization in the target population</t>
+  </si>
+  <si>
+    <t>To understand the quantity of water consumed in households of the target population</t>
+  </si>
+  <si>
+    <t>To understand the quality of water consumed in households of the target population</t>
+  </si>
+  <si>
+    <t>To understand the the level and sources of food availability in the target population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the level and sources of water in the target population </t>
+  </si>
+  <si>
+    <t>HH Water Availability</t>
+  </si>
+  <si>
+    <t>HH Water Accessibility</t>
+  </si>
+  <si>
+    <t>HH Water Utilization</t>
+  </si>
+  <si>
+    <t>HH Water Stability</t>
+  </si>
+  <si>
+    <t>Household Income Sources</t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to water utilization in the target population</t>
+  </si>
+  <si>
+    <t>To understand the level of stability/reliability of water sources in the target population</t>
+  </si>
+  <si>
+    <t>To understand the level of stability/reliability of food sources in the target population</t>
+  </si>
+  <si>
+    <t>To understand the level of access and barriers to water in the target population</t>
+  </si>
+  <si>
+    <t>Household Coping Strategies</t>
+  </si>
+  <si>
+    <t>Access to Food Assistance</t>
+  </si>
+  <si>
+    <t>Asset Ownership</t>
+  </si>
+  <si>
+    <t>To understand the level and sources of household income in the target population</t>
+  </si>
+  <si>
+    <t>To understand the types of coping strategies used to access basic goods and services in the target population</t>
+  </si>
+  <si>
+    <t>To understand the level and types of household assets owned by households in the target population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the extent to which the target population has access to emergency food assistance </t>
+  </si>
+  <si>
+    <t>To understand the extent to which the target population has access to adequate shelter</t>
+  </si>
+  <si>
+    <t>Adequate Shelter</t>
+  </si>
+  <si>
+    <t>Mosquito Net Coverage</t>
+  </si>
+  <si>
+    <t>To understand the level of ownership of mosquito nets in the target population</t>
+  </si>
+  <si>
+    <t>Mosquito Net Utilization</t>
+  </si>
+  <si>
+    <t>To understand the level of mosquito net utilization in the target population</t>
+  </si>
+  <si>
+    <t>Shelter Sleeping Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the level of crowdedness in the target population </t>
+  </si>
+  <si>
+    <t>To understand the type and extent of shelter sleeping problems in the target population</t>
+  </si>
+  <si>
+    <t>Livelihood Availability</t>
+  </si>
+  <si>
+    <t>Livelihood Accessibility</t>
+  </si>
+  <si>
+    <t>Market Availability</t>
+  </si>
+  <si>
+    <t>Market Accessibility</t>
+  </si>
+  <si>
+    <t>Market Functionality</t>
+  </si>
+  <si>
+    <t>Purchasing Power</t>
+  </si>
+  <si>
+    <t>Community Water Availability</t>
+  </si>
+  <si>
+    <t>Community Water Accessibility</t>
+  </si>
+  <si>
+    <t>Community Water Utilization</t>
+  </si>
+  <si>
+    <t>To estimate the quality of individual water consumption at point of use</t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to water utilization at the community level in the target population</t>
+  </si>
+  <si>
+    <t>To understand the quality of water access at the point of collection</t>
+  </si>
+  <si>
+    <t>Water Quality at Point of Collection</t>
+  </si>
+  <si>
+    <t>To understand the availability of livelihoods in the community of the target population</t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to accessing livelihoods in the target population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the availability of markets for the target population </t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to market access for the target population</t>
+  </si>
+  <si>
+    <t>To understand the extent and barriers to purchasing power for the target population</t>
+  </si>
+  <si>
+    <t>To understand the extent of market functionality in the target population</t>
+  </si>
+  <si>
+    <t>To understand the barriers and issues related to water access at the community level in the target population</t>
+  </si>
+  <si>
+    <t>To understand the level of availability of water at the community level in the target population</t>
+  </si>
+  <si>
+    <t>CMAM Availability</t>
+  </si>
+  <si>
+    <t>CMAM Coverage</t>
+  </si>
+  <si>
+    <t>TSFP Coverage</t>
+  </si>
+  <si>
+    <t>CMAM Performance</t>
+  </si>
+  <si>
+    <t>CMAM Care Seeking Behaviours</t>
+  </si>
+  <si>
+    <t>Coverage of Nutrition Preventive Services</t>
+  </si>
+  <si>
+    <t>To understand the level of availability of therapeutic nutrition services in the target population</t>
+  </si>
+  <si>
+    <t>To estimate the proxy coverage of therapeutic nutrition services for children under-5 years of age in the target population</t>
+  </si>
+  <si>
+    <t>To estimate the proxy coverage of therapeutic nutrition services for pregnant and lactating women in the target population</t>
+  </si>
+  <si>
+    <t>To understand the quality of therapeutic nutrition service provision for nutrition facilities in the target population</t>
+  </si>
+  <si>
+    <t>To understand the care seeking behaviours for nutrition services in the target population</t>
+  </si>
+  <si>
+    <t>To estimate the coverage of preventive nutrition services in the target population</t>
+  </si>
+  <si>
+    <t>Presence of Primary Health Care Facilities</t>
+  </si>
+  <si>
+    <t>Barriers to Healthcare Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To understand the barriers and issues related to </t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E7D8C5-59DB-465F-80B7-E6C364678A90}">
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
@@ -1143,15 +1773,17 @@
     <col min="6" max="6" width="55.42578125" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" customWidth="1"/>
     <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="54" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" customWidth="1"/>
-    <col min="11" max="11" width="17.140625" customWidth="1"/>
-    <col min="12" max="13" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="98.42578125" customWidth="1"/>
+    <col min="10" max="10" width="68.85546875" customWidth="1"/>
+    <col min="11" max="11" width="35.5703125" customWidth="1"/>
+    <col min="12" max="12" width="26.5703125" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B1" t="s">
         <v>62</v>
@@ -1187,13 +1819,16 @@
         <v>134</v>
       </c>
       <c r="M1" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="N1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>110</v>
       </c>
@@ -1221,17 +1856,20 @@
       <c r="I2" t="s">
         <v>140</v>
       </c>
+      <c r="J2" t="s">
+        <v>264</v>
+      </c>
       <c r="K2" t="s">
-        <v>143</v>
+        <v>311</v>
       </c>
       <c r="L2" t="s">
-        <v>144</v>
+        <v>312</v>
       </c>
       <c r="N2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>110</v>
       </c>
@@ -1257,10 +1895,22 @@
         <v>11002</v>
       </c>
       <c r="I3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="J3" t="s">
+        <v>282</v>
+      </c>
+      <c r="K3" t="s">
+        <v>313</v>
+      </c>
+      <c r="L3" t="s">
+        <v>314</v>
+      </c>
+      <c r="N3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>110</v>
       </c>
@@ -1286,10 +1936,22 @@
         <v>11003</v>
       </c>
       <c r="I4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="J4" t="s">
+        <v>283</v>
+      </c>
+      <c r="K4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L4" t="s">
+        <v>265</v>
+      </c>
+      <c r="N4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>110</v>
       </c>
@@ -1315,10 +1977,22 @@
         <v>11004</v>
       </c>
       <c r="I5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J5" t="s">
+        <v>267</v>
+      </c>
+      <c r="K5" t="s">
+        <v>268</v>
+      </c>
+      <c r="L5" t="s">
+        <v>270</v>
+      </c>
+      <c r="N5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>110</v>
       </c>
@@ -1344,10 +2018,22 @@
         <v>11005</v>
       </c>
       <c r="I6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="J6" t="s">
+        <v>269</v>
+      </c>
+      <c r="K6" t="s">
+        <v>307</v>
+      </c>
+      <c r="L6" t="s">
+        <v>306</v>
+      </c>
+      <c r="N6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>110</v>
       </c>
@@ -1373,10 +2059,22 @@
         <v>11006</v>
       </c>
       <c r="I7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="J7" t="s">
+        <v>271</v>
+      </c>
+      <c r="K7" t="s">
+        <v>308</v>
+      </c>
+      <c r="L7" t="s">
+        <v>315</v>
+      </c>
+      <c r="N7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>110</v>
       </c>
@@ -1402,10 +2100,22 @@
         <v>11007</v>
       </c>
       <c r="I8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="J8" t="s">
+        <v>272</v>
+      </c>
+      <c r="K8" t="s">
+        <v>308</v>
+      </c>
+      <c r="L8" t="s">
+        <v>316</v>
+      </c>
+      <c r="N8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>110</v>
       </c>
@@ -1431,10 +2141,22 @@
         <v>11008</v>
       </c>
       <c r="I9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="J9" t="s">
+        <v>281</v>
+      </c>
+      <c r="K9" t="s">
+        <v>309</v>
+      </c>
+      <c r="L9" t="s">
+        <v>315</v>
+      </c>
+      <c r="N9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>110</v>
       </c>
@@ -1460,10 +2182,22 @@
         <v>11009</v>
       </c>
       <c r="I10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="J10" t="s">
+        <v>284</v>
+      </c>
+      <c r="K10" t="s">
+        <v>285</v>
+      </c>
+      <c r="L10" t="s">
+        <v>315</v>
+      </c>
+      <c r="N10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>120</v>
       </c>
@@ -1480,7 +2214,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G11" t="s">
         <v>139</v>
@@ -1489,10 +2223,22 @@
         <v>12001</v>
       </c>
       <c r="I11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="J11" t="s">
+        <v>286</v>
+      </c>
+      <c r="K11" t="s">
+        <v>296</v>
+      </c>
+      <c r="L11" t="s">
+        <v>270</v>
+      </c>
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>120</v>
       </c>
@@ -1509,7 +2255,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
         <v>139</v>
@@ -1518,10 +2264,22 @@
         <v>12002</v>
       </c>
       <c r="I12" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+      <c r="J12" t="s">
+        <v>287</v>
+      </c>
+      <c r="K12" t="s">
+        <v>295</v>
+      </c>
+      <c r="L12" t="s">
+        <v>270</v>
+      </c>
+      <c r="N12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>120</v>
       </c>
@@ -1538,7 +2296,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G13" t="s">
         <v>139</v>
@@ -1547,10 +2305,22 @@
         <v>12003</v>
       </c>
       <c r="I13" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="J13" t="s">
+        <v>288</v>
+      </c>
+      <c r="K13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L13" t="s">
+        <v>270</v>
+      </c>
+      <c r="N13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>120</v>
       </c>
@@ -1567,7 +2337,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G14" t="s">
         <v>139</v>
@@ -1576,10 +2346,22 @@
         <v>12004</v>
       </c>
       <c r="I14" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="J14" t="s">
+        <v>289</v>
+      </c>
+      <c r="K14" t="s">
+        <v>294</v>
+      </c>
+      <c r="L14" t="s">
+        <v>270</v>
+      </c>
+      <c r="N14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>120</v>
       </c>
@@ -1596,7 +2378,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G15" t="s">
         <v>139</v>
@@ -1605,12 +2387,24 @@
         <v>12005</v>
       </c>
       <c r="I15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="J15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K15" t="s">
+        <v>310</v>
+      </c>
+      <c r="L15" t="s">
+        <v>270</v>
+      </c>
+      <c r="N15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
         <v>63</v>
@@ -1619,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>4</v>
+        <v>201</v>
       </c>
       <c r="E16" t="s">
-        <v>4</v>
+        <v>149</v>
       </c>
       <c r="F16" t="s">
         <v>150</v>
@@ -1631,13 +2425,25 @@
         <v>139</v>
       </c>
       <c r="H16">
-        <v>12006</v>
+        <v>13001</v>
       </c>
       <c r="I16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="J16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K16" t="s">
+        <v>292</v>
+      </c>
+      <c r="L16" t="s">
+        <v>306</v>
+      </c>
+      <c r="N16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>130</v>
       </c>
@@ -1648,25 +2454,40 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F17" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G17" t="s">
         <v>139</v>
       </c>
       <c r="H17">
-        <v>13001</v>
+        <v>13002</v>
       </c>
       <c r="I17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="J17" t="s">
+        <v>299</v>
+      </c>
+      <c r="K17" t="s">
+        <v>300</v>
+      </c>
+      <c r="L17" t="s">
+        <v>301</v>
+      </c>
+      <c r="N17" t="s">
+        <v>138</v>
+      </c>
+      <c r="O17" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>130</v>
       </c>
@@ -1677,25 +2498,37 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E18" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F18" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G18" t="s">
         <v>139</v>
       </c>
       <c r="H18">
-        <v>13002</v>
+        <v>13003</v>
       </c>
       <c r="I18" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="J18" t="s">
+        <v>303</v>
+      </c>
+      <c r="K18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L18" t="s">
+        <v>306</v>
+      </c>
+      <c r="N18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>130</v>
       </c>
@@ -1706,25 +2539,37 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G19" t="s">
         <v>139</v>
       </c>
       <c r="H19">
-        <v>13003</v>
+        <v>13004</v>
       </c>
       <c r="I19" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="J19" t="s">
+        <v>305</v>
+      </c>
+      <c r="K19" t="s">
+        <v>319</v>
+      </c>
+      <c r="L19" t="s">
+        <v>306</v>
+      </c>
+      <c r="N19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>130</v>
       </c>
@@ -1735,25 +2580,37 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E20" t="s">
+        <v>149</v>
+      </c>
+      <c r="F20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G20" t="s">
+        <v>139</v>
+      </c>
+      <c r="H20">
+        <v>13005</v>
+      </c>
+      <c r="I20" t="s">
         <v>159</v>
       </c>
-      <c r="F20" t="s">
-        <v>160</v>
-      </c>
-      <c r="G20" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20">
-        <v>13004</v>
-      </c>
-      <c r="I20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" t="s">
+        <v>317</v>
+      </c>
+      <c r="K20" t="s">
+        <v>318</v>
+      </c>
+      <c r="L20" t="s">
+        <v>306</v>
+      </c>
+      <c r="N20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>130</v>
       </c>
@@ -1764,25 +2621,37 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E21" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F21" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" t="s">
+        <v>139</v>
+      </c>
+      <c r="H21">
+        <v>13006</v>
+      </c>
+      <c r="I21" t="s">
         <v>160</v>
       </c>
-      <c r="G21" t="s">
-        <v>139</v>
-      </c>
-      <c r="H21">
-        <v>13005</v>
-      </c>
-      <c r="I21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" t="s">
+        <v>320</v>
+      </c>
+      <c r="K21" t="s">
+        <v>321</v>
+      </c>
+      <c r="L21" t="s">
+        <v>306</v>
+      </c>
+      <c r="N21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>130</v>
       </c>
@@ -1793,27 +2662,39 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E22" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F22" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G22" t="s">
         <v>139</v>
       </c>
       <c r="H22">
-        <v>13006</v>
+        <v>13007</v>
       </c>
       <c r="I22" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="J22" t="s">
+        <v>322</v>
+      </c>
+      <c r="K22" t="s">
+        <v>323</v>
+      </c>
+      <c r="L22" t="s">
+        <v>306</v>
+      </c>
+      <c r="N22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B23" t="s">
         <v>63</v>
@@ -1822,25 +2703,37 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="G23" t="s">
         <v>139</v>
       </c>
       <c r="H23">
-        <v>13007</v>
+        <v>14001</v>
       </c>
       <c r="I23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="J23" t="s">
+        <v>325</v>
+      </c>
+      <c r="K23" t="s">
+        <v>326</v>
+      </c>
+      <c r="L23" t="s">
+        <v>328</v>
+      </c>
+      <c r="N23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>140</v>
       </c>
@@ -1851,54 +2744,78 @@
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="E24" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="F24" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="G24" t="s">
         <v>139</v>
       </c>
       <c r="H24">
-        <v>14001</v>
+        <v>14002</v>
       </c>
       <c r="I24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+      <c r="J24" t="s">
+        <v>324</v>
+      </c>
+      <c r="K24" t="s">
+        <v>327</v>
+      </c>
+      <c r="L24" t="s">
+        <v>328</v>
+      </c>
+      <c r="N24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>215</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G25" t="s">
         <v>139</v>
       </c>
       <c r="H25">
-        <v>14002</v>
+        <v>15001</v>
       </c>
       <c r="I25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="J25" t="s">
+        <v>331</v>
+      </c>
+      <c r="K25" t="s">
+        <v>334</v>
+      </c>
+      <c r="L25" t="s">
+        <v>315</v>
+      </c>
+      <c r="N25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>150</v>
       </c>
@@ -1915,19 +2832,31 @@
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>221</v>
+        <v>167</v>
       </c>
       <c r="G26" t="s">
         <v>139</v>
       </c>
       <c r="H26">
-        <v>15001</v>
+        <v>15002</v>
       </c>
       <c r="I26" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="J26" t="s">
+        <v>332</v>
+      </c>
+      <c r="K26" t="s">
+        <v>333</v>
+      </c>
+      <c r="L26" t="s">
+        <v>335</v>
+      </c>
+      <c r="N26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>150</v>
       </c>
@@ -1944,21 +2873,33 @@
         <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="G27" t="s">
         <v>139</v>
       </c>
       <c r="H27">
-        <v>15002</v>
+        <v>15003</v>
       </c>
       <c r="I27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="J27" t="s">
+        <v>336</v>
+      </c>
+      <c r="K27" t="s">
+        <v>333</v>
+      </c>
+      <c r="L27" t="s">
+        <v>335</v>
+      </c>
+      <c r="N27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
         <v>64</v>
@@ -1970,22 +2911,34 @@
         <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="F28" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="G28" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="H28">
-        <v>15003</v>
+        <v>16001</v>
       </c>
       <c r="I28" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="J28" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" t="s">
+        <v>337</v>
+      </c>
+      <c r="L28" t="s">
+        <v>338</v>
+      </c>
+      <c r="N28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>160</v>
       </c>
@@ -1999,22 +2952,34 @@
         <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H29">
-        <v>16001</v>
+        <v>16002</v>
       </c>
       <c r="I29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="J29" t="s">
+        <v>341</v>
+      </c>
+      <c r="K29" t="s">
+        <v>342</v>
+      </c>
+      <c r="L29" t="s">
+        <v>343</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>160</v>
       </c>
@@ -2028,22 +2993,34 @@
         <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H30">
-        <v>16002</v>
+        <v>16003</v>
       </c>
       <c r="I30" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="J30" t="s">
+        <v>344</v>
+      </c>
+      <c r="K30" t="s">
+        <v>347</v>
+      </c>
+      <c r="L30" t="s">
+        <v>338</v>
+      </c>
+      <c r="N30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>160</v>
       </c>
@@ -2057,51 +3034,75 @@
         <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F31" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H31">
-        <v>16003</v>
+        <v>16004</v>
       </c>
       <c r="I31" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="J31" t="s">
+        <v>345</v>
+      </c>
+      <c r="K31" t="s">
+        <v>346</v>
+      </c>
+      <c r="L31" t="s">
+        <v>348</v>
+      </c>
+      <c r="N31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="H32">
-        <v>16004</v>
+        <v>17001</v>
       </c>
       <c r="I32" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="J32" t="s">
+        <v>353</v>
+      </c>
+      <c r="K32" t="s">
+        <v>349</v>
+      </c>
+      <c r="L32" t="s">
+        <v>351</v>
+      </c>
+      <c r="N32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>170</v>
       </c>
@@ -2115,265 +3116,406 @@
         <v>103</v>
       </c>
       <c r="E33" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F33" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="G33" t="s">
         <v>139</v>
       </c>
       <c r="H33">
-        <v>17001</v>
+        <v>17002</v>
       </c>
       <c r="I33" t="s">
+        <v>173</v>
+      </c>
+      <c r="J33" t="s">
+        <v>354</v>
+      </c>
+      <c r="K33" t="s">
+        <v>350</v>
+      </c>
+      <c r="L33" t="s">
+        <v>352</v>
+      </c>
+      <c r="N33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>180</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" t="s">
+        <v>273</v>
+      </c>
+      <c r="F34" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34">
+        <v>18001</v>
+      </c>
+      <c r="I34" t="s">
+        <v>260</v>
+      </c>
+      <c r="J34" t="s">
+        <v>355</v>
+      </c>
+      <c r="K34" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34" t="s">
+        <v>313</v>
+      </c>
+      <c r="N34" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>180</v>
+      </c>
+      <c r="B35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" t="s">
+        <v>274</v>
+      </c>
+      <c r="F35" t="s">
+        <v>359</v>
+      </c>
+      <c r="G35" t="s">
+        <v>139</v>
+      </c>
+      <c r="H35">
+        <v>18002</v>
+      </c>
+      <c r="I35" t="s">
+        <v>259</v>
+      </c>
+      <c r="J35" t="s">
+        <v>358</v>
+      </c>
+      <c r="K35" t="s">
+        <v>360</v>
+      </c>
+      <c r="L35" t="s">
+        <v>313</v>
+      </c>
+      <c r="N35" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>177</v>
+      </c>
+      <c r="D36" t="s">
+        <v>175</v>
+      </c>
+      <c r="E36" t="s">
+        <v>279</v>
+      </c>
+      <c r="F36" t="s">
+        <v>276</v>
+      </c>
+      <c r="G36" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36">
+        <v>19001</v>
+      </c>
+      <c r="I36" t="s">
+        <v>357</v>
+      </c>
+      <c r="J36" t="s">
+        <v>361</v>
+      </c>
+      <c r="K36" t="s">
+        <v>362</v>
+      </c>
+      <c r="L36" t="s">
+        <v>363</v>
+      </c>
+      <c r="N36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>190</v>
+      </c>
+      <c r="B37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" t="s">
+        <v>177</v>
+      </c>
+      <c r="D37" t="s">
+        <v>176</v>
+      </c>
+      <c r="E37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F37" t="s">
+        <v>412</v>
+      </c>
+      <c r="G37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>170</v>
-      </c>
-      <c r="B34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" t="s">
-        <v>103</v>
-      </c>
-      <c r="E34" t="s">
-        <v>182</v>
-      </c>
-      <c r="F34" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" t="s">
-        <v>139</v>
-      </c>
-      <c r="H34">
-        <v>17002</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="E38" t="s">
+        <v>278</v>
+      </c>
+      <c r="F38" t="s">
+        <v>277</v>
+      </c>
+      <c r="G38" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>200</v>
+      </c>
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>170</v>
-      </c>
-      <c r="B35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" t="s">
-        <v>103</v>
-      </c>
-      <c r="D35" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" t="s">
-        <v>182</v>
-      </c>
-      <c r="F35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" t="s">
-        <v>139</v>
-      </c>
-      <c r="H35">
-        <v>17003</v>
-      </c>
-      <c r="I35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>170</v>
-      </c>
-      <c r="B36" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" t="s">
-        <v>182</v>
-      </c>
-      <c r="F36" t="s">
-        <v>183</v>
-      </c>
-      <c r="G36" t="s">
-        <v>139</v>
-      </c>
-      <c r="H36">
-        <v>17004</v>
-      </c>
-      <c r="I36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>170</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" t="s">
-        <v>183</v>
-      </c>
-      <c r="G37" t="s">
-        <v>139</v>
-      </c>
-      <c r="H37">
-        <v>17005</v>
-      </c>
-      <c r="I37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>170</v>
-      </c>
-      <c r="B38" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" t="s">
-        <v>103</v>
-      </c>
-      <c r="D38" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" t="s">
-        <v>182</v>
-      </c>
-      <c r="F38" t="s">
-        <v>183</v>
-      </c>
-      <c r="G38" t="s">
-        <v>139</v>
-      </c>
-      <c r="H38">
-        <v>17006</v>
-      </c>
-      <c r="I38" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>180</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="E39" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" t="s">
+        <v>364</v>
+      </c>
+      <c r="G39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H39">
+        <v>20001</v>
+      </c>
+      <c r="I39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>200</v>
+      </c>
+      <c r="B40" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" t="s">
+        <v>186</v>
+      </c>
+      <c r="F40" t="s">
+        <v>364</v>
+      </c>
+      <c r="G40" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40">
+        <v>20002</v>
+      </c>
+      <c r="I40" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
         <v>73</v>
       </c>
-      <c r="C39" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>180</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C41" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="s">
+        <v>365</v>
+      </c>
+      <c r="E41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" t="s">
+        <v>366</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41">
+        <v>21001</v>
+      </c>
+      <c r="I41" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>210</v>
+      </c>
+      <c r="B42" t="s">
         <v>73</v>
       </c>
-      <c r="C40" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>190</v>
-      </c>
-      <c r="B41" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" t="s">
-        <v>192</v>
-      </c>
-      <c r="D41" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>190</v>
-      </c>
-      <c r="B42" t="s">
-        <v>67</v>
-      </c>
       <c r="C42" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D42" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="E42" t="s">
+        <v>211</v>
+      </c>
+      <c r="F42" t="s">
+        <v>366</v>
+      </c>
+      <c r="G42" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42">
+        <v>21002</v>
+      </c>
+      <c r="I42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D43" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="E43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s">
+        <v>366</v>
+      </c>
+      <c r="G43" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43">
+        <v>21003</v>
+      </c>
+      <c r="I43" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="D44" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="E44" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" t="s">
+        <v>367</v>
+      </c>
+      <c r="G44" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44">
+        <v>21101</v>
+      </c>
+      <c r="I44" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s">
         <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D45" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="E45" t="s">
+        <v>212</v>
+      </c>
+      <c r="F45" t="s">
+        <v>367</v>
+      </c>
+      <c r="G45" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45">
+        <v>21102</v>
+      </c>
+      <c r="I45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>220</v>
       </c>
@@ -2381,13 +3523,28 @@
         <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="E46" t="s">
+        <v>368</v>
+      </c>
+      <c r="F46" t="s">
+        <v>376</v>
+      </c>
+      <c r="G46" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46">
+        <v>22001</v>
+      </c>
+      <c r="I46" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>230</v>
       </c>
@@ -2395,1358 +3552,2326 @@
         <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="E47" t="s">
+        <v>369</v>
+      </c>
+      <c r="F47" t="s">
+        <v>372</v>
+      </c>
+      <c r="G47" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47">
+        <v>23001</v>
+      </c>
+      <c r="I47" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B48" t="s">
         <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D48" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="E48" t="s">
+        <v>369</v>
+      </c>
+      <c r="F48" t="s">
+        <v>372</v>
+      </c>
+      <c r="G48" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48">
+        <v>23002</v>
+      </c>
+      <c r="I48" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s">
         <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D49" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="E49" t="s">
+        <v>369</v>
+      </c>
+      <c r="F49" t="s">
+        <v>372</v>
+      </c>
+      <c r="G49" t="s">
+        <v>139</v>
+      </c>
+      <c r="H49">
+        <v>23003</v>
+      </c>
+      <c r="I49" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50">
+        <v>240</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" t="s">
+        <v>370</v>
+      </c>
+      <c r="F50" t="s">
+        <v>373</v>
+      </c>
+      <c r="G50" t="s">
+        <v>139</v>
+      </c>
+      <c r="H50">
+        <v>24001</v>
+      </c>
+      <c r="I50" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>240</v>
+      </c>
+      <c r="B51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" t="s">
+        <v>370</v>
+      </c>
+      <c r="F51" t="s">
+        <v>373</v>
+      </c>
+      <c r="G51" t="s">
+        <v>139</v>
+      </c>
+      <c r="H51">
+        <v>24002</v>
+      </c>
+      <c r="I51" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>240</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+      <c r="C52" t="s">
+        <v>179</v>
+      </c>
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" t="s">
+        <v>370</v>
+      </c>
+      <c r="F52" t="s">
+        <v>373</v>
+      </c>
+      <c r="G52" t="s">
+        <v>139</v>
+      </c>
+      <c r="H52">
+        <v>24003</v>
+      </c>
+      <c r="I52" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>240</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" t="s">
+        <v>179</v>
+      </c>
+      <c r="D53" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" t="s">
+        <v>370</v>
+      </c>
+      <c r="F53" t="s">
+        <v>373</v>
+      </c>
+      <c r="G53" t="s">
+        <v>139</v>
+      </c>
+      <c r="H53">
+        <v>24004</v>
+      </c>
+      <c r="I53" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>250</v>
+      </c>
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
+        <v>184</v>
+      </c>
+      <c r="E54" t="s">
+        <v>371</v>
+      </c>
+      <c r="F54" t="s">
+        <v>385</v>
+      </c>
+      <c r="G54" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>260</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C55" t="s">
         <v>75</v>
       </c>
-      <c r="D50" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="D55" t="s">
+        <v>180</v>
+      </c>
+      <c r="E55" t="s">
+        <v>211</v>
+      </c>
+      <c r="F55" t="s">
+        <v>374</v>
+      </c>
+      <c r="G55" t="s">
+        <v>139</v>
+      </c>
+      <c r="H55">
+        <v>26001</v>
+      </c>
+      <c r="I55" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>261</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
+        <v>180</v>
+      </c>
+      <c r="E56" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" t="s">
+        <v>375</v>
+      </c>
+      <c r="G56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>270</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B57" t="s">
         <v>67</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C57" t="s">
         <v>75</v>
       </c>
-      <c r="D51" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>280</v>
-      </c>
-      <c r="B52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D52" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>290</v>
-      </c>
-      <c r="B53" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>300</v>
-      </c>
-      <c r="B54" t="s">
-        <v>67</v>
-      </c>
-      <c r="C54" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>310</v>
-      </c>
-      <c r="B55" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" t="s">
-        <v>87</v>
-      </c>
-      <c r="D55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>320</v>
-      </c>
-      <c r="B56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" t="s">
-        <v>87</v>
-      </c>
-      <c r="D56" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>330</v>
-      </c>
-      <c r="B57" t="s">
-        <v>73</v>
-      </c>
-      <c r="C57" t="s">
-        <v>87</v>
-      </c>
       <c r="D57" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="E57" t="s">
+        <v>378</v>
+      </c>
+      <c r="F57" t="s">
+        <v>377</v>
+      </c>
+      <c r="G57" t="s">
+        <v>139</v>
+      </c>
+      <c r="H57">
+        <v>27001</v>
+      </c>
+      <c r="I57" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
       <c r="C58" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="E58" t="s">
+        <v>378</v>
+      </c>
+      <c r="F58" t="s">
+        <v>377</v>
+      </c>
+      <c r="G58" t="s">
+        <v>139</v>
+      </c>
+      <c r="H58">
+        <v>27002</v>
+      </c>
+      <c r="I58" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="E59" t="s">
+        <v>379</v>
+      </c>
+      <c r="F59" t="s">
+        <v>386</v>
+      </c>
+      <c r="G59" t="s">
+        <v>139</v>
+      </c>
+      <c r="H59">
+        <v>28001</v>
+      </c>
+      <c r="I59" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
       </c>
       <c r="C60" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D60" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="E60" t="s">
+        <v>380</v>
+      </c>
+      <c r="F60" t="s">
+        <v>383</v>
+      </c>
+      <c r="G60" t="s">
+        <v>139</v>
+      </c>
+      <c r="H60">
+        <v>29001</v>
+      </c>
+      <c r="I60" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>202</v>
+        <v>75</v>
       </c>
       <c r="D61" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="E61" t="s">
+        <v>380</v>
+      </c>
+      <c r="F61" t="s">
+        <v>383</v>
+      </c>
+      <c r="G61" t="s">
+        <v>139</v>
+      </c>
+      <c r="H61">
+        <v>29002</v>
+      </c>
+      <c r="I61" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62">
+        <v>290</v>
+      </c>
+      <c r="B62" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" t="s">
         <v>380</v>
       </c>
-      <c r="B62" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" t="s">
-        <v>202</v>
-      </c>
-      <c r="D62" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F62" t="s">
+        <v>383</v>
+      </c>
+      <c r="G62" t="s">
+        <v>139</v>
+      </c>
+      <c r="H62">
+        <v>29003</v>
+      </c>
+      <c r="I62" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="E63" t="s">
+        <v>380</v>
+      </c>
+      <c r="F63" t="s">
+        <v>383</v>
+      </c>
+      <c r="G63" t="s">
+        <v>139</v>
+      </c>
+      <c r="H63">
+        <v>29004</v>
+      </c>
+      <c r="I63" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D64" t="s">
-        <v>197</v>
+        <v>184</v>
+      </c>
+      <c r="E64" t="s">
+        <v>381</v>
+      </c>
+      <c r="F64" t="s">
+        <v>384</v>
+      </c>
+      <c r="G64" t="s">
+        <v>139</v>
+      </c>
+      <c r="H64">
+        <v>30001</v>
+      </c>
+      <c r="I64" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>410</v>
+        <v>310</v>
       </c>
       <c r="B65" t="s">
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
-        <v>207</v>
+        <v>188</v>
+      </c>
+      <c r="E65" t="s">
+        <v>382</v>
+      </c>
+      <c r="F65" t="s">
+        <v>390</v>
+      </c>
+      <c r="G65" t="s">
+        <v>139</v>
+      </c>
+      <c r="H65">
+        <v>31001</v>
+      </c>
+      <c r="I65" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>420</v>
+        <v>320</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D66" t="s">
-        <v>196</v>
+        <v>88</v>
+      </c>
+      <c r="E66" t="s">
+        <v>387</v>
+      </c>
+      <c r="F66" t="s">
+        <v>391</v>
+      </c>
+      <c r="G66" t="s">
+        <v>139</v>
+      </c>
+      <c r="H66">
+        <v>32001</v>
+      </c>
+      <c r="I66" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>430</v>
+        <v>321</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D67" t="s">
-        <v>197</v>
+        <v>88</v>
+      </c>
+      <c r="E67" t="s">
+        <v>388</v>
+      </c>
+      <c r="F67" t="s">
+        <v>393</v>
+      </c>
+      <c r="G67" t="s">
+        <v>139</v>
+      </c>
+      <c r="H67">
+        <v>32101</v>
+      </c>
+      <c r="I67" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>440</v>
+        <v>330</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D68" t="s">
-        <v>191</v>
+        <v>189</v>
+      </c>
+      <c r="E68" t="s">
+        <v>389</v>
+      </c>
+      <c r="F68" t="s">
+        <v>392</v>
+      </c>
+      <c r="G68" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="B69" t="s">
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D69" t="s">
-        <v>198</v>
+        <v>190</v>
+      </c>
+      <c r="E69" t="s">
+        <v>395</v>
+      </c>
+      <c r="F69" t="s">
+        <v>394</v>
+      </c>
+      <c r="G69" t="s">
+        <v>139</v>
+      </c>
+      <c r="H69">
+        <v>34001</v>
+      </c>
+      <c r="I69" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D70" t="s">
-        <v>196</v>
+        <v>190</v>
+      </c>
+      <c r="E70" t="s">
+        <v>395</v>
+      </c>
+      <c r="F70" t="s">
+        <v>394</v>
+      </c>
+      <c r="G70" t="s">
+        <v>139</v>
+      </c>
+      <c r="H70">
+        <v>34002</v>
+      </c>
+      <c r="I70" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>470</v>
+        <v>340</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C71" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D71" t="s">
-        <v>197</v>
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>395</v>
+      </c>
+      <c r="F71" t="s">
+        <v>394</v>
+      </c>
+      <c r="G71" t="s">
+        <v>139</v>
+      </c>
+      <c r="H71">
+        <v>34003</v>
+      </c>
+      <c r="I71" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>480</v>
+        <v>350</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D72" t="s">
         <v>191</v>
       </c>
+      <c r="E72" t="s">
+        <v>396</v>
+      </c>
+      <c r="F72" t="s">
+        <v>397</v>
+      </c>
+      <c r="G72" t="s">
+        <v>139</v>
+      </c>
+      <c r="H72">
+        <v>35001</v>
+      </c>
+      <c r="I72" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>490</v>
+        <v>351</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D73" t="s">
-        <v>198</v>
+        <v>191</v>
+      </c>
+      <c r="E73" t="s">
+        <v>398</v>
+      </c>
+      <c r="F73" t="s">
+        <v>399</v>
+      </c>
+      <c r="G73" t="s">
+        <v>139</v>
+      </c>
+      <c r="H73">
+        <v>35101</v>
+      </c>
+      <c r="I73" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="D74" t="s">
-        <v>105</v>
+        <v>110</v>
+      </c>
+      <c r="E74" t="s">
+        <v>129</v>
+      </c>
+      <c r="F74" t="s">
+        <v>401</v>
+      </c>
+      <c r="G74" t="s">
+        <v>139</v>
+      </c>
+      <c r="H74">
+        <v>36001</v>
+      </c>
+      <c r="I74" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>510</v>
+        <v>360</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C75" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D75" t="s">
-        <v>196</v>
+        <v>110</v>
+      </c>
+      <c r="E75" t="s">
+        <v>400</v>
+      </c>
+      <c r="F75" t="s">
+        <v>402</v>
+      </c>
+      <c r="G75" t="s">
+        <v>139</v>
+      </c>
+      <c r="H75">
+        <v>36002</v>
+      </c>
+      <c r="I75" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>520</v>
+        <v>370</v>
       </c>
       <c r="B76" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C76" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
-      </c>
-      <c r="H76">
-        <v>52001</v>
-      </c>
-      <c r="I76" t="s">
-        <v>228</v>
+        <v>181</v>
+      </c>
+      <c r="E76" t="s">
+        <v>403</v>
+      </c>
+      <c r="F76" t="s">
+        <v>416</v>
+      </c>
+      <c r="G76" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>520</v>
+        <v>380</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D77" t="s">
-        <v>197</v>
-      </c>
-      <c r="H77">
-        <v>52002</v>
-      </c>
-      <c r="I77" t="s">
-        <v>227</v>
+        <v>182</v>
+      </c>
+      <c r="E77" t="s">
+        <v>404</v>
+      </c>
+      <c r="F77" t="s">
+        <v>417</v>
+      </c>
+      <c r="G77" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>530</v>
+        <v>390</v>
       </c>
       <c r="B78" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>191</v>
+        <v>181</v>
+      </c>
+      <c r="E78" t="s">
+        <v>405</v>
+      </c>
+      <c r="F78" t="s">
+        <v>418</v>
+      </c>
+      <c r="G78" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>540</v>
+        <v>400</v>
       </c>
       <c r="B79" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C79" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D79" t="s">
-        <v>198</v>
+        <v>182</v>
+      </c>
+      <c r="E79" t="s">
+        <v>406</v>
+      </c>
+      <c r="F79" t="s">
+        <v>419</v>
+      </c>
+      <c r="G79" t="s">
+        <v>139</v>
       </c>
       <c r="H79">
-        <v>54001</v>
+        <v>40001</v>
       </c>
       <c r="I79" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>540</v>
+        <v>401</v>
       </c>
       <c r="B80" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D80" t="s">
-        <v>198</v>
+        <v>182</v>
+      </c>
+      <c r="E80" t="s">
+        <v>408</v>
+      </c>
+      <c r="F80" t="s">
+        <v>420</v>
+      </c>
+      <c r="G80" t="s">
+        <v>139</v>
       </c>
       <c r="H80">
-        <v>54002</v>
+        <v>40101</v>
       </c>
       <c r="I80" t="s">
-        <v>223</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>410</v>
+      </c>
+      <c r="B81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" t="s">
+        <v>407</v>
+      </c>
+      <c r="F81" t="s">
+        <v>421</v>
+      </c>
+      <c r="G81" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>420</v>
+      </c>
+      <c r="B82" t="s">
+        <v>67</v>
+      </c>
+      <c r="C82" t="s">
+        <v>93</v>
+      </c>
+      <c r="D82" t="s">
+        <v>181</v>
+      </c>
+      <c r="E82" t="s">
+        <v>409</v>
+      </c>
+      <c r="F82" t="s">
+        <v>423</v>
+      </c>
+      <c r="G82" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>430</v>
+      </c>
+      <c r="B83" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" t="s">
+        <v>93</v>
+      </c>
+      <c r="D83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" t="s">
+        <v>410</v>
+      </c>
+      <c r="F83" t="s">
+        <v>422</v>
+      </c>
+      <c r="G83" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>550</v>
+        <v>440</v>
       </c>
       <c r="B84" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C84" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
-      </c>
-      <c r="H84">
-        <v>55001</v>
-      </c>
-      <c r="I84" t="s">
-        <v>224</v>
+        <v>176</v>
+      </c>
+      <c r="E84" t="s">
+        <v>415</v>
+      </c>
+      <c r="F84" t="s">
+        <v>414</v>
+      </c>
+      <c r="G84" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C85" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D85" t="s">
-        <v>105</v>
-      </c>
-      <c r="H85">
-        <v>55002</v>
-      </c>
-      <c r="I85" t="s">
-        <v>225</v>
+        <v>183</v>
+      </c>
+      <c r="E85" t="s">
+        <v>411</v>
+      </c>
+      <c r="F85" t="s">
+        <v>413</v>
+      </c>
+      <c r="G85" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>550</v>
+        <v>460</v>
       </c>
       <c r="B86" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D86" t="s">
-        <v>105</v>
-      </c>
-      <c r="H86">
-        <v>55003</v>
-      </c>
-      <c r="I86" t="s">
-        <v>226</v>
+        <v>181</v>
+      </c>
+      <c r="E86" t="s">
+        <v>424</v>
+      </c>
+      <c r="F86" t="s">
+        <v>430</v>
+      </c>
+      <c r="G86" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>470</v>
+      </c>
+      <c r="B87" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" t="s">
+        <v>71</v>
+      </c>
+      <c r="D87" t="s">
+        <v>182</v>
+      </c>
+      <c r="E87" t="s">
+        <v>425</v>
+      </c>
+      <c r="F87" t="s">
+        <v>431</v>
+      </c>
+      <c r="G87" t="s">
+        <v>139</v>
+      </c>
+      <c r="H87">
+        <v>47001</v>
+      </c>
+      <c r="I87" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>560</v>
+        <v>470</v>
       </c>
       <c r="B88" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C88" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D88" t="s">
-        <v>208</v>
+        <v>182</v>
+      </c>
+      <c r="E88" t="s">
+        <v>426</v>
+      </c>
+      <c r="F88" t="s">
+        <v>432</v>
+      </c>
+      <c r="G88" t="s">
+        <v>139</v>
+      </c>
+      <c r="H88">
+        <v>47002</v>
+      </c>
+      <c r="I88" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>570</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C89" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>176</v>
+      </c>
+      <c r="E89" t="s">
+        <v>427</v>
+      </c>
+      <c r="F89" t="s">
+        <v>433</v>
+      </c>
+      <c r="G89" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="B90" t="s">
-        <v>209</v>
+        <v>66</v>
       </c>
       <c r="C90" t="s">
-        <v>209</v>
+        <v>71</v>
       </c>
       <c r="D90" t="s">
-        <v>209</v>
+        <v>176</v>
+      </c>
+      <c r="E90" t="s">
+        <v>427</v>
+      </c>
+      <c r="F90" t="s">
+        <v>433</v>
+      </c>
+      <c r="G90" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="B91" t="s">
-        <v>210</v>
+        <v>66</v>
       </c>
       <c r="C91" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="D91" t="s">
-        <v>210</v>
+        <v>176</v>
+      </c>
+      <c r="E91" t="s">
+        <v>427</v>
+      </c>
+      <c r="F91" t="s">
+        <v>433</v>
+      </c>
+      <c r="G91" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="B92" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="C92" t="s">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="D92" t="s">
-        <v>211</v>
+        <v>176</v>
+      </c>
+      <c r="E92" t="s">
+        <v>427</v>
+      </c>
+      <c r="F92" t="s">
+        <v>433</v>
+      </c>
+      <c r="G92" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93">
+        <v>490</v>
+      </c>
+      <c r="B93" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" t="s">
+        <v>71</v>
+      </c>
+      <c r="D93" t="s">
+        <v>183</v>
+      </c>
+      <c r="E93" t="s">
+        <v>428</v>
+      </c>
+      <c r="F93" t="s">
+        <v>434</v>
+      </c>
+      <c r="G93" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>500</v>
+      </c>
+      <c r="B94" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94" t="s">
+        <v>71</v>
+      </c>
+      <c r="D94" t="s">
+        <v>105</v>
+      </c>
+      <c r="E94" t="s">
+        <v>429</v>
+      </c>
+      <c r="F94" t="s">
+        <v>435</v>
+      </c>
+      <c r="G94" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>510</v>
+      </c>
+      <c r="B95" t="s">
+        <v>64</v>
+      </c>
+      <c r="C95" t="s">
+        <v>70</v>
+      </c>
+      <c r="D95" t="s">
+        <v>181</v>
+      </c>
+      <c r="E95" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>520</v>
+      </c>
+      <c r="B96" t="s">
+        <v>64</v>
+      </c>
+      <c r="C96" t="s">
+        <v>70</v>
+      </c>
+      <c r="D96" t="s">
+        <v>182</v>
+      </c>
+      <c r="E96" t="s">
+        <v>437</v>
+      </c>
+      <c r="F96" t="s">
+        <v>438</v>
+      </c>
+      <c r="H96">
+        <v>52001</v>
+      </c>
+      <c r="I96" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>520</v>
+      </c>
+      <c r="B97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D97" t="s">
+        <v>182</v>
+      </c>
+      <c r="H97">
+        <v>52002</v>
+      </c>
+      <c r="I97" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>520</v>
+      </c>
+      <c r="B98" t="s">
+        <v>64</v>
+      </c>
+      <c r="C98" t="s">
+        <v>70</v>
+      </c>
+      <c r="D98" t="s">
+        <v>182</v>
+      </c>
+      <c r="H98">
+        <v>52003</v>
+      </c>
+      <c r="I98" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>530</v>
+      </c>
+      <c r="B99" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" t="s">
+        <v>70</v>
+      </c>
+      <c r="D99" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>540</v>
+      </c>
+      <c r="B100" t="s">
+        <v>64</v>
+      </c>
+      <c r="C100" t="s">
+        <v>70</v>
+      </c>
+      <c r="D100" t="s">
+        <v>183</v>
+      </c>
+      <c r="H100">
+        <v>54001</v>
+      </c>
+      <c r="I100" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>540</v>
+      </c>
+      <c r="B101" t="s">
+        <v>64</v>
+      </c>
+      <c r="C101" t="s">
+        <v>70</v>
+      </c>
+      <c r="D101" t="s">
+        <v>183</v>
+      </c>
+      <c r="H101">
+        <v>54002</v>
+      </c>
+      <c r="I101" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>540</v>
+      </c>
+      <c r="B102" t="s">
+        <v>64</v>
+      </c>
+      <c r="C102" t="s">
+        <v>70</v>
+      </c>
+      <c r="D102" t="s">
+        <v>183</v>
+      </c>
+      <c r="H102">
+        <v>54003</v>
+      </c>
+      <c r="I102" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>550</v>
+      </c>
+      <c r="B103" t="s">
+        <v>64</v>
+      </c>
+      <c r="C103" t="s">
+        <v>70</v>
+      </c>
+      <c r="D103" t="s">
+        <v>105</v>
+      </c>
+      <c r="H103">
+        <v>55001</v>
+      </c>
+      <c r="I103" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>550</v>
+      </c>
+      <c r="B104" t="s">
+        <v>64</v>
+      </c>
+      <c r="C104" t="s">
+        <v>70</v>
+      </c>
+      <c r="D104" t="s">
+        <v>105</v>
+      </c>
+      <c r="H104">
+        <v>55002</v>
+      </c>
+      <c r="I104" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>550</v>
+      </c>
+      <c r="B105" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" t="s">
+        <v>70</v>
+      </c>
+      <c r="D105" t="s">
+        <v>105</v>
+      </c>
+      <c r="H105">
+        <v>55003</v>
+      </c>
+      <c r="I105" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>560</v>
+      </c>
+      <c r="B106" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" t="s">
+        <v>79</v>
+      </c>
+      <c r="D106" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>570</v>
+      </c>
+      <c r="B107" t="s">
+        <v>67</v>
+      </c>
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" t="s">
+        <v>78</v>
+      </c>
+      <c r="H107">
+        <v>57001</v>
+      </c>
+      <c r="I107" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>570</v>
+      </c>
+      <c r="B108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C108" t="s">
+        <v>79</v>
+      </c>
+      <c r="D108" t="s">
+        <v>78</v>
+      </c>
+      <c r="H108">
+        <v>57002</v>
+      </c>
+      <c r="I108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>580</v>
+      </c>
+      <c r="B109" t="s">
+        <v>194</v>
+      </c>
+      <c r="C109" t="s">
+        <v>194</v>
+      </c>
+      <c r="D109" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>590</v>
+      </c>
+      <c r="B110" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" t="s">
+        <v>195</v>
+      </c>
+      <c r="D110" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>600</v>
+      </c>
+      <c r="B111" t="s">
+        <v>196</v>
+      </c>
+      <c r="C111" t="s">
+        <v>196</v>
+      </c>
+      <c r="D111" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112">
         <v>610</v>
       </c>
-      <c r="B93" t="s">
-        <v>212</v>
-      </c>
-      <c r="C93" t="s">
-        <v>212</v>
-      </c>
-      <c r="D93" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B119" t="s">
+      <c r="B112" t="s">
+        <v>197</v>
+      </c>
+      <c r="C112" t="s">
+        <v>197</v>
+      </c>
+      <c r="D112" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
         <v>64</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C138" t="s">
         <v>70</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D138" t="s">
         <v>9</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E138" t="s">
         <v>10</v>
       </c>
-      <c r="F119" t="s">
-        <v>157</v>
-      </c>
-      <c r="G119" t="s">
-        <v>139</v>
-      </c>
-      <c r="H119">
+      <c r="F138" t="s">
+        <v>147</v>
+      </c>
+      <c r="G138" t="s">
+        <v>139</v>
+      </c>
+      <c r="H138">
         <v>14001</v>
       </c>
-      <c r="I119" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B120" t="s">
+      <c r="I138" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
         <v>64</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C139" t="s">
         <v>70</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D139" t="s">
         <v>9</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E139" t="s">
         <v>10</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F139" t="s">
         <v>8</v>
       </c>
-      <c r="G120" t="s">
-        <v>139</v>
-      </c>
-      <c r="H120">
+      <c r="G139" t="s">
+        <v>139</v>
+      </c>
+      <c r="H139">
         <v>14002</v>
       </c>
-      <c r="I120" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B121" t="s">
+      <c r="I139" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
         <v>64</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C140" t="s">
         <v>70</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D140" t="s">
         <v>21</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E140" t="s">
         <v>23</v>
       </c>
-      <c r="F121" t="s">
+      <c r="F140" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B125" t="s">
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
         <v>65</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C144" t="s">
         <v>73</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D144" t="s">
         <v>27</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E144" t="s">
         <v>12</v>
       </c>
-      <c r="F125" t="s">
+      <c r="F144" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B126" t="s">
-        <v>65</v>
-      </c>
-      <c r="C126" t="s">
-        <v>73</v>
-      </c>
-      <c r="D126" t="s">
-        <v>28</v>
-      </c>
-      <c r="E126" t="s">
-        <v>13</v>
-      </c>
-      <c r="F126" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B127" t="s">
-        <v>64</v>
-      </c>
-      <c r="C127" t="s">
-        <v>70</v>
-      </c>
-      <c r="D127" t="s">
-        <v>16</v>
-      </c>
-      <c r="E127" t="s">
-        <v>25</v>
-      </c>
-      <c r="F127" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B128" t="s">
-        <v>66</v>
-      </c>
-      <c r="C128" t="s">
-        <v>71</v>
-      </c>
-      <c r="D128" t="s">
-        <v>15</v>
-      </c>
-      <c r="E128" t="s">
-        <v>26</v>
-      </c>
-      <c r="F128" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B129" t="s">
-        <v>66</v>
-      </c>
-      <c r="C129" t="s">
-        <v>71</v>
-      </c>
-      <c r="D129" t="s">
-        <v>22</v>
-      </c>
-      <c r="E129" t="s">
-        <v>24</v>
-      </c>
-      <c r="F129" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B130" t="s">
-        <v>65</v>
-      </c>
-      <c r="C130" t="s">
-        <v>73</v>
-      </c>
-      <c r="D130" t="s">
-        <v>31</v>
-      </c>
-      <c r="E130" t="s">
-        <v>39</v>
-      </c>
-      <c r="F130" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B131" t="s">
-        <v>65</v>
-      </c>
-      <c r="C131" t="s">
-        <v>73</v>
-      </c>
-      <c r="D131" t="s">
-        <v>31</v>
-      </c>
-      <c r="E131" t="s">
-        <v>38</v>
-      </c>
-      <c r="F131" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B132" t="s">
-        <v>65</v>
-      </c>
-      <c r="C132" t="s">
-        <v>73</v>
-      </c>
-      <c r="D132" t="s">
-        <v>28</v>
-      </c>
-      <c r="E132" t="s">
-        <v>49</v>
-      </c>
-      <c r="F132" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B133" t="s">
-        <v>65</v>
-      </c>
-      <c r="C133" t="s">
-        <v>73</v>
-      </c>
-      <c r="D133" t="s">
-        <v>51</v>
-      </c>
-      <c r="E133" t="s">
-        <v>128</v>
-      </c>
-      <c r="F133" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B134" t="s">
-        <v>65</v>
-      </c>
-      <c r="C134" t="s">
-        <v>73</v>
-      </c>
-      <c r="D134" t="s">
-        <v>51</v>
-      </c>
-      <c r="E134" t="s">
-        <v>50</v>
-      </c>
-      <c r="F134" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B135" t="s">
-        <v>65</v>
-      </c>
-      <c r="C135" t="s">
-        <v>73</v>
-      </c>
-      <c r="D135" t="s">
-        <v>35</v>
-      </c>
-      <c r="E135" t="s">
-        <v>52</v>
-      </c>
-      <c r="F135" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B136" t="s">
-        <v>67</v>
-      </c>
-      <c r="C136" t="s">
-        <v>75</v>
-      </c>
-      <c r="D136" t="s">
-        <v>53</v>
-      </c>
-      <c r="E136" t="s">
-        <v>54</v>
-      </c>
-      <c r="F136" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B137" t="s">
-        <v>67</v>
-      </c>
-      <c r="C137" t="s">
-        <v>75</v>
-      </c>
-      <c r="D137" t="s">
-        <v>53</v>
-      </c>
-      <c r="E137" t="s">
-        <v>55</v>
-      </c>
-      <c r="F137" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B138" t="s">
-        <v>67</v>
-      </c>
-      <c r="C138" t="s">
-        <v>75</v>
-      </c>
-      <c r="D138" t="s">
-        <v>57</v>
-      </c>
-      <c r="E138" t="s">
-        <v>58</v>
-      </c>
-      <c r="F138" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B139" t="s">
-        <v>67</v>
-      </c>
-      <c r="C139" t="s">
-        <v>75</v>
-      </c>
-      <c r="D139" t="s">
-        <v>60</v>
-      </c>
-      <c r="E139" t="s">
-        <v>59</v>
-      </c>
-      <c r="F139" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B140" t="s">
-        <v>67</v>
-      </c>
-      <c r="C140" t="s">
-        <v>75</v>
-      </c>
-      <c r="D140" t="s">
-        <v>76</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G140" s="1"/>
-    </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B141" t="s">
-        <v>67</v>
-      </c>
-      <c r="C141" t="s">
-        <v>75</v>
-      </c>
-      <c r="D141" t="s">
-        <v>76</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B142" t="s">
-        <v>67</v>
-      </c>
-      <c r="C142" t="s">
-        <v>75</v>
-      </c>
-      <c r="D142" t="s">
-        <v>77</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G142" s="1"/>
-    </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B143" t="s">
-        <v>67</v>
-      </c>
-      <c r="C143" t="s">
-        <v>79</v>
-      </c>
-      <c r="D143" t="s">
-        <v>78</v>
-      </c>
-      <c r="E143" t="s">
-        <v>80</v>
-      </c>
-      <c r="F143" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B144" t="s">
-        <v>67</v>
-      </c>
-      <c r="C144" t="s">
-        <v>79</v>
-      </c>
-      <c r="D144" t="s">
-        <v>81</v>
-      </c>
-      <c r="E144" t="s">
-        <v>82</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G144" s="2"/>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C145" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D145" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="E145" t="s">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="F145" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C146" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D146" t="s">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="E146" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="F146" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C147" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D147" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E147" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="148" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C148" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D148" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="E148" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="F148" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C149" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D149" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E149" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="F149" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C150" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D150" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E150" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="F150" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C151" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D151" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="E151" t="s">
-        <v>100</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G151" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="F151" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="152" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C152" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D152" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E152" t="s">
-        <v>101</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G152" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="F152" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C153" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D153" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="E153" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="F153" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="154" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C154" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D154" t="s">
-        <v>103</v>
+        <v>35</v>
+      </c>
+      <c r="E154" t="s">
+        <v>52</v>
+      </c>
+      <c r="F154" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C155" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D155" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="E155" t="s">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="F155" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="156" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C156" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D156" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="E156" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="F156" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="157" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C157" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D157" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="E157" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="F157" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C158" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D158" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E158" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="F158" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C159" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D159" t="s">
-        <v>83</v>
-      </c>
-      <c r="E159" t="s">
-        <v>122</v>
-      </c>
-      <c r="F159" t="s">
-        <v>121</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G159" s="1"/>
     </row>
     <row r="160" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
+        <v>67</v>
+      </c>
+      <c r="C160" t="s">
+        <v>75</v>
+      </c>
+      <c r="D160" t="s">
+        <v>76</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G160" s="1"/>
+    </row>
+    <row r="161" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>67</v>
+      </c>
+      <c r="C161" t="s">
+        <v>75</v>
+      </c>
+      <c r="D161" t="s">
+        <v>77</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G161" s="1"/>
+    </row>
+    <row r="162" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>67</v>
+      </c>
+      <c r="C162" t="s">
+        <v>79</v>
+      </c>
+      <c r="D162" t="s">
+        <v>78</v>
+      </c>
+      <c r="E162" t="s">
+        <v>80</v>
+      </c>
+      <c r="F162" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>67</v>
+      </c>
+      <c r="C163" t="s">
+        <v>79</v>
+      </c>
+      <c r="D163" t="s">
+        <v>81</v>
+      </c>
+      <c r="E163" t="s">
+        <v>82</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G163" s="2"/>
+    </row>
+    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>63</v>
+      </c>
+      <c r="C164" t="s">
+        <v>87</v>
+      </c>
+      <c r="D164" t="s">
+        <v>88</v>
+      </c>
+      <c r="E164" t="s">
+        <v>89</v>
+      </c>
+      <c r="F164" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>63</v>
+      </c>
+      <c r="C165" t="s">
+        <v>72</v>
+      </c>
+      <c r="D165" t="s">
+        <v>90</v>
+      </c>
+      <c r="E165" t="s">
+        <v>125</v>
+      </c>
+      <c r="F165" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>63</v>
+      </c>
+      <c r="C166" t="s">
+        <v>72</v>
+      </c>
+      <c r="D166" t="s">
+        <v>90</v>
+      </c>
+      <c r="E166" t="s">
+        <v>127</v>
+      </c>
+      <c r="F166" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>63</v>
+      </c>
+      <c r="C167" t="s">
+        <v>72</v>
+      </c>
+      <c r="D167" t="s">
+        <v>91</v>
+      </c>
+      <c r="E167" t="s">
+        <v>92</v>
+      </c>
+      <c r="F167" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>67</v>
+      </c>
+      <c r="C168" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" t="s">
+        <v>74</v>
+      </c>
+      <c r="E168" t="s">
+        <v>94</v>
+      </c>
+      <c r="F168" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>67</v>
+      </c>
+      <c r="C169" t="s">
+        <v>93</v>
+      </c>
+      <c r="D169" t="s">
+        <v>74</v>
+      </c>
+      <c r="E169" t="s">
+        <v>97</v>
+      </c>
+      <c r="F169" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>67</v>
+      </c>
+      <c r="C170" t="s">
+        <v>79</v>
+      </c>
+      <c r="D170" t="s">
+        <v>78</v>
+      </c>
+      <c r="E170" t="s">
+        <v>100</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G170" s="2"/>
+    </row>
+    <row r="171" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>67</v>
+      </c>
+      <c r="C171" t="s">
+        <v>79</v>
+      </c>
+      <c r="D171" t="s">
+        <v>78</v>
+      </c>
+      <c r="E171" t="s">
+        <v>101</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G171" s="2"/>
+    </row>
+    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>66</v>
+      </c>
+      <c r="C172" t="s">
+        <v>103</v>
+      </c>
+      <c r="D172" t="s">
+        <v>103</v>
+      </c>
+      <c r="E172" t="s">
+        <v>104</v>
+      </c>
+      <c r="F172" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="173" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>66</v>
+      </c>
+      <c r="C173" t="s">
+        <v>103</v>
+      </c>
+      <c r="D173" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="174" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>64</v>
+      </c>
+      <c r="C174" t="s">
+        <v>70</v>
+      </c>
+      <c r="D174" t="s">
+        <v>105</v>
+      </c>
+      <c r="E174" t="s">
+        <v>106</v>
+      </c>
+      <c r="F174" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="175" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>64</v>
+      </c>
+      <c r="C175" t="s">
+        <v>70</v>
+      </c>
+      <c r="D175" t="s">
+        <v>105</v>
+      </c>
+      <c r="E175" t="s">
+        <v>107</v>
+      </c>
+      <c r="F175" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="176" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>64</v>
+      </c>
+      <c r="C176" t="s">
+        <v>70</v>
+      </c>
+      <c r="D176" t="s">
+        <v>105</v>
+      </c>
+      <c r="E176" t="s">
+        <v>108</v>
+      </c>
+      <c r="F176" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>64</v>
+      </c>
+      <c r="C177" t="s">
+        <v>85</v>
+      </c>
+      <c r="D177" t="s">
+        <v>85</v>
+      </c>
+      <c r="E177" t="s">
+        <v>109</v>
+      </c>
+      <c r="F177" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
         <v>84</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C178" t="s">
         <v>86</v>
       </c>
-      <c r="D160" t="s">
+      <c r="D178" t="s">
         <v>83</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E178" t="s">
+        <v>122</v>
+      </c>
+      <c r="F178" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>84</v>
+      </c>
+      <c r="C179" t="s">
+        <v>86</v>
+      </c>
+      <c r="D179" t="s">
+        <v>83</v>
+      </c>
+      <c r="E179" t="s">
         <v>123</v>
       </c>
-      <c r="F160" t="s">
+      <c r="F179" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B161" t="s">
+    <row r="180" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
         <v>64</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C180" t="s">
         <v>86</v>
       </c>
-      <c r="D161" t="s">
+      <c r="D180" t="s">
         <v>118</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E180" t="s">
         <v>120</v>
       </c>
-      <c r="F161" t="s">
+      <c r="F180" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B162" t="s">
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
         <v>84</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C181" t="s">
         <v>86</v>
       </c>
-      <c r="D162" t="s">
+      <c r="D181" t="s">
         <v>110</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E181" t="s">
         <v>129</v>
       </c>
-      <c r="F162" t="s">
+      <c r="F181" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>